--- a/Input/C2_C1_Database.xlsx
+++ b/Input/C2_C1_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/audreycampeau/Documents/DATA/TROLLBERGET DITCH/R/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D63BCF9-CD7F-5A49-A024-A1F3CCCD439C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5BE902-4CF1-214F-B7B3-37F1FF3BC5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="760" windowWidth="28860" windowHeight="18880" xr2:uid="{485FF81E-12AE-0147-B2E3-2425FDCEEDC1}"/>
+    <workbookView xWindow="2380" yWindow="4780" windowWidth="29000" windowHeight="18880" xr2:uid="{485FF81E-12AE-0147-B2E3-2425FDCEEDC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Aligned for DC_Q" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <author>tc={29DAC5EA-70B6-3640-865B-8B41FA28A66D}</author>
   </authors>
   <commentList>
-    <comment ref="AW3" authorId="0" shapeId="0" xr:uid="{29DAC5EA-70B6-3640-865B-8B41FA28A66D}">
+    <comment ref="AS3" authorId="0" shapeId="0" xr:uid="{29DAC5EA-70B6-3640-865B-8B41FA28A66D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="233">
   <si>
     <t>SUERC-95052</t>
   </si>
@@ -462,9 +462,6 @@
     <t>Averge between (2021-08-02 and 2021-08-31)</t>
   </si>
   <si>
-    <t>TimeStamp_Meteo</t>
-  </si>
-  <si>
     <t>TA</t>
   </si>
   <si>
@@ -504,27 +501,12 @@
     <t>Station Name</t>
   </si>
   <si>
-    <t>TimeStamp_Q</t>
-  </si>
-  <si>
     <t>Q</t>
   </si>
   <si>
-    <t>Q_m3d</t>
-  </si>
-  <si>
-    <t>q_md</t>
-  </si>
-  <si>
-    <t>q_md_filled</t>
-  </si>
-  <si>
     <t>Treatment</t>
   </si>
   <si>
-    <t>Treatment_4</t>
-  </si>
-  <si>
     <t>Site_id_chem</t>
   </si>
   <si>
@@ -774,7 +756,22 @@
     <t>DOC</t>
   </si>
   <si>
-    <t>Pristine</t>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>HYG</t>
+  </si>
+  <si>
+    <t>HED</t>
+  </si>
+  <si>
+    <t>TimeStamp</t>
+  </si>
+  <si>
+    <t>q_int_mmd</t>
+  </si>
+  <si>
+    <t>PreDisturbance</t>
   </si>
 </sst>
 </file>
@@ -806,13 +803,14 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -834,6 +832,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -859,7 +869,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -962,6 +972,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2254,7 +2266,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="AW3" dT="2025-08-08T21:01:44.07" personId="{878B036A-EAFB-2140-964E-9D70B91E6A1B}" id="{29DAC5EA-70B6-3640-865B-8B41FA28A66D}">
+  <threadedComment ref="AS3" dT="2025-08-08T21:01:44.07" personId="{878B036A-EAFB-2140-964E-9D70B91E6A1B}" id="{29DAC5EA-70B6-3640-865B-8B41FA28A66D}">
     <text>copied from DIC.both measurements before and after showed DIC=CO2</text>
   </threadedComment>
 </ThreadedComments>
@@ -2270,7 +2282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88D8429F-1787-6B4C-8256-E985632EFC6B}">
-  <dimension ref="B1:DB23"/>
+  <dimension ref="A1:CX23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -2288,7 +2300,7 @@
     <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.83203125" customWidth="1"/>
     <col min="20" max="20" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
@@ -2312,9 +2324,9 @@
     <col min="40" max="40" width="7" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="8.83203125" bestFit="1" customWidth="1"/>
@@ -2375,3500 +2387,4214 @@
     <col min="106" max="106" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:102" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1" t="s">
         <v>129</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>130</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>131</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>132</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>133</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>134</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>135</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>136</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>137</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>138</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>139</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>140</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>141</v>
-      </c>
-      <c r="O1" t="s">
-        <v>142</v>
       </c>
       <c r="P1" t="s">
         <v>110</v>
       </c>
       <c r="Q1" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1" t="s">
+        <v>231</v>
+      </c>
+      <c r="S1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T1" t="s">
         <v>143</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>144</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>145</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>146</v>
       </c>
-      <c r="U1" t="s">
-        <v>61</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>147</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>148</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>149</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>150</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>151</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>152</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>153</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>154</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>155</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>156</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>157</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>158</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>159</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>160</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>161</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>162</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>163</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>164</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>165</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>166</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>167</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>168</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>169</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>170</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>171</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>172</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>173</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>174</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>175</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>176</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>177</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>178</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>179</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>180</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>181</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>182</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>183</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>184</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>185</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>186</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>187</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>188</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>189</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>190</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>191</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>192</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>193</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>194</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>195</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BU1" t="s">
         <v>196</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BV1" t="s">
         <v>197</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BW1" t="s">
         <v>198</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BX1" t="s">
         <v>199</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BY1" t="s">
         <v>200</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BZ1" t="s">
         <v>201</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="CA1" t="s">
         <v>202</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CB1" t="s">
         <v>203</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CC1" t="s">
         <v>204</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CD1" t="s">
         <v>205</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CE1" t="s">
         <v>206</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CF1" t="s">
         <v>207</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CG1" t="s">
         <v>208</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CH1" t="s">
         <v>209</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CI1" t="s">
         <v>210</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CJ1" t="s">
         <v>211</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CK1" t="s">
         <v>212</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CL1" t="s">
         <v>213</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CM1" t="s">
         <v>214</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CN1" t="s">
         <v>215</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CO1" t="s">
         <v>216</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CP1" t="s">
         <v>217</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CQ1" t="s">
         <v>218</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CR1" t="s">
         <v>219</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CS1" t="s">
         <v>220</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CT1" t="s">
         <v>221</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CU1" t="s">
         <v>222</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CV1" t="s">
         <v>223</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CW1" t="s">
         <v>224</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CX1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13">
+        <v>43901</v>
+      </c>
+      <c r="C2">
+        <v>0.1</v>
+      </c>
+      <c r="D2">
+        <v>1.3</v>
+      </c>
+      <c r="E2">
+        <v>-1.3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G2">
+        <v>0.8</v>
+      </c>
+      <c r="H2">
+        <v>2.1</v>
+      </c>
+      <c r="I2">
+        <v>2.1</v>
+      </c>
+      <c r="J2">
+        <v>6.7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O2" t="s">
+        <v>228</v>
+      </c>
+      <c r="P2" s="48">
+        <v>43901</v>
+      </c>
+      <c r="R2">
+        <v>0.21519058331941299</v>
+      </c>
+      <c r="S2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T2" t="s">
+        <v>232</v>
+      </c>
+      <c r="U2" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="V2" s="34">
+        <v>5.83</v>
+      </c>
+      <c r="W2" s="34">
+        <v>30</v>
+      </c>
+      <c r="X2" s="34">
+        <v>13.09</v>
+      </c>
+      <c r="Y2" s="34">
+        <v>41.3</v>
+      </c>
+      <c r="Z2" s="34">
+        <v>0.30570000000000003</v>
+      </c>
+      <c r="AA2" s="34">
+        <v>14.38</v>
+      </c>
+      <c r="AB2" s="34">
+        <v>1.72</v>
+      </c>
+      <c r="AC2" s="34">
+        <v>1724.06</v>
+      </c>
+      <c r="AL2" s="34">
+        <v>911.19330000000002</v>
+      </c>
+      <c r="AN2" s="34">
+        <v>-12.980596999999999</v>
+      </c>
+      <c r="AP2" s="35">
+        <v>1.0370098728674</v>
+      </c>
+      <c r="AQ2" s="35">
+        <v>968.93639867929005</v>
+      </c>
+      <c r="AR2" s="35"/>
+      <c r="AS2" s="35">
+        <v>0.87635720039961695</v>
+      </c>
+      <c r="BB2" s="47">
+        <f>AS2</f>
+        <v>0.87635720039961695</v>
+      </c>
+      <c r="BC2" s="47">
+        <f>AP2</f>
+        <v>1.0370098728674</v>
+      </c>
+      <c r="BD2" s="47">
+        <f>V2</f>
+        <v>5.83</v>
+      </c>
+      <c r="BF2" s="47">
+        <f>X2</f>
+        <v>13.09</v>
+      </c>
+      <c r="BV2" s="47">
+        <f>AN2</f>
+        <v>-12.980596999999999</v>
+      </c>
+      <c r="BZ2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="CA2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="CB2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CC2">
+        <v>71</v>
+      </c>
+      <c r="CD2">
+        <v>2020</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH2" s="3">
+        <v>101.0497</v>
+      </c>
+      <c r="CI2" s="3">
+        <v>0.46279999999999999</v>
+      </c>
+      <c r="CJ2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL2" s="3">
+        <v>8.84</v>
+      </c>
+      <c r="CM2" s="5">
+        <v>-28.68</v>
+      </c>
+      <c r="CP2" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="CQ2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="CR2" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CS2" s="14">
+        <v>96.564899999999994</v>
+      </c>
+      <c r="CT2" s="15">
+        <v>0.44290000000000002</v>
+      </c>
+      <c r="CU2" s="16">
+        <v>281</v>
+      </c>
+      <c r="CV2" s="16">
+        <v>37</v>
+      </c>
+      <c r="CW2" s="15">
+        <v>3.52</v>
+      </c>
+      <c r="CX2" s="17">
+        <v>-18.423999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13">
+        <v>43948</v>
+      </c>
+      <c r="C3">
+        <v>0.7</v>
+      </c>
+      <c r="D3">
+        <v>3.6</v>
+      </c>
+      <c r="E3">
+        <v>-2.8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G3">
+        <v>0.5</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>11.3</v>
+      </c>
+      <c r="J3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K3">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>227</v>
+      </c>
+      <c r="M3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="N3">
+        <v>6.5</v>
+      </c>
+      <c r="O3" t="s">
+        <v>228</v>
+      </c>
+      <c r="P3" s="48">
+        <v>43948</v>
+      </c>
+      <c r="R3">
+        <v>2.0148391226740499</v>
+      </c>
+      <c r="S3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T3" t="s">
+        <v>232</v>
+      </c>
+      <c r="U3" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="V3" s="41">
+        <v>4.91</v>
+      </c>
+      <c r="W3" s="41">
+        <v>30</v>
+      </c>
+      <c r="X3" s="41">
+        <v>22.903300000000002</v>
+      </c>
+      <c r="Y3" s="41">
+        <v>96.99</v>
+      </c>
+      <c r="Z3" s="41">
+        <v>0.46860000000000002</v>
+      </c>
+      <c r="AA3" s="41">
+        <v>8.58</v>
+      </c>
+      <c r="AB3" s="41">
+        <v>2.72</v>
+      </c>
+      <c r="AC3" s="41">
+        <v>1205.71</v>
+      </c>
+      <c r="AL3" s="41">
+        <v>1095.5672999999999</v>
+      </c>
+      <c r="AN3" s="41">
+        <v>-13.3948</v>
+      </c>
+      <c r="AP3" s="42">
+        <v>0.77274029767522401</v>
+      </c>
+      <c r="AQ3" s="42"/>
+      <c r="AR3" s="42"/>
+      <c r="AS3" s="42">
+        <v>0.77</v>
+      </c>
+      <c r="BB3" s="47">
+        <f t="shared" ref="BB3:BB22" si="0">AS3</f>
+        <v>0.77</v>
+      </c>
+      <c r="BC3" s="47">
+        <f t="shared" ref="BC3:BC22" si="1">AP3</f>
+        <v>0.77274029767522401</v>
+      </c>
+      <c r="BD3" s="47">
+        <f t="shared" ref="BD3:BD22" si="2">V3</f>
+        <v>4.91</v>
+      </c>
+      <c r="BF3" s="47">
+        <f t="shared" ref="BF3:BF22" si="3">X3</f>
+        <v>22.903300000000002</v>
+      </c>
+      <c r="BV3" s="47">
+        <f t="shared" ref="BV3:BV23" si="4">AN3</f>
+        <v>-13.3948</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="CA3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="CC3">
+        <v>118</v>
+      </c>
+      <c r="CD3">
+        <v>2020</v>
+      </c>
+      <c r="CG3" t="s">
         <v>226</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CH3" s="3">
+        <v>104.86020000000001</v>
+      </c>
+      <c r="CI3" s="3">
+        <v>0.48080000000000001</v>
+      </c>
+      <c r="CJ3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL3" s="5">
+        <v>14.7</v>
+      </c>
+      <c r="CM3" s="5">
+        <v>-28.754999999999999</v>
+      </c>
+      <c r="CR3" s="9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13">
+        <v>44071</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>16.7</v>
+      </c>
+      <c r="E4">
+        <v>3.4</v>
+      </c>
+      <c r="F4" t="s">
         <v>227</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="G4">
+        <v>10.6</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>12.1</v>
+      </c>
+      <c r="J4">
+        <v>9.6</v>
+      </c>
+      <c r="K4">
+        <v>27</v>
+      </c>
+      <c r="L4">
+        <v>6</v>
+      </c>
+      <c r="M4">
+        <v>1.2</v>
+      </c>
+      <c r="N4">
+        <v>3.8</v>
+      </c>
+      <c r="O4" t="s">
         <v>228</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>229</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>230</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P2" s="13">
-        <v>43901</v>
-      </c>
-      <c r="R2">
-        <v>0.29887056499999998</v>
-      </c>
-      <c r="S2">
-        <f>R2/1000*60*60*24</f>
-        <v>25.822416816</v>
-      </c>
-      <c r="T2">
-        <f>S2/1200000</f>
-        <v>2.1518680680000001E-5</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="P4" s="48">
+        <v>44071</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4" t="s">
         <v>3</v>
       </c>
-      <c r="V2">
-        <f>T2</f>
-        <v>2.1518680680000001E-5</v>
-      </c>
-      <c r="W2" t="s">
-        <v>233</v>
-      </c>
-      <c r="X2" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y2" s="33" t="s">
+      <c r="T4" t="s">
+        <v>232</v>
+      </c>
+      <c r="U4" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="34">
-        <v>5.83</v>
-      </c>
-      <c r="AA2" s="34">
+      <c r="V4" s="41">
+        <v>5.86</v>
+      </c>
+      <c r="W4" s="41">
         <v>30</v>
       </c>
-      <c r="AB2" s="34">
-        <v>13.09</v>
-      </c>
-      <c r="AC2" s="34">
-        <v>41.3</v>
-      </c>
-      <c r="AD2" s="34">
-        <v>0.30570000000000003</v>
-      </c>
-      <c r="AE2" s="34">
-        <v>14.38</v>
-      </c>
-      <c r="AF2" s="34">
-        <v>1.72</v>
-      </c>
-      <c r="AG2" s="34">
-        <v>1724.06</v>
-      </c>
-      <c r="AP2" s="34">
-        <v>911.19330000000002</v>
-      </c>
-      <c r="AR2" s="34">
-        <v>-12.980596999999999</v>
-      </c>
-      <c r="AT2" s="35">
-        <v>1.0370098728674</v>
-      </c>
-      <c r="AU2" s="35">
-        <v>968.93639867929005</v>
-      </c>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="35">
-        <v>0.87635720039961695</v>
-      </c>
-      <c r="BF2" s="47">
-        <f>AW2</f>
-        <v>0.87635720039961695</v>
-      </c>
-      <c r="BG2" s="47">
-        <f>AT2</f>
-        <v>1.0370098728674</v>
-      </c>
-      <c r="BH2" s="47">
-        <f>Z2</f>
-        <v>5.83</v>
-      </c>
-      <c r="BJ2" s="47">
-        <f>AB2</f>
-        <v>13.09</v>
-      </c>
-      <c r="BZ2" s="47">
-        <f>AR2</f>
-        <v>-12.980596999999999</v>
-      </c>
-      <c r="CD2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="CE2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CF2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="CH2">
-        <v>2020</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>232</v>
-      </c>
-      <c r="CL2" s="3">
-        <v>101.0497</v>
-      </c>
-      <c r="CM2" s="3">
-        <v>0.46279999999999999</v>
-      </c>
-      <c r="CN2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP2" s="3">
-        <v>8.84</v>
-      </c>
-      <c r="CQ2" s="5">
-        <v>-28.68</v>
-      </c>
-      <c r="CT2" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="CU2" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="CV2" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW2" s="14">
-        <v>96.564899999999994</v>
-      </c>
-      <c r="CX2" s="15">
-        <v>0.44290000000000002</v>
-      </c>
-      <c r="CY2" s="16">
-        <v>281</v>
-      </c>
-      <c r="CZ2" s="16">
-        <v>37</v>
-      </c>
-      <c r="DA2" s="15">
-        <v>3.52</v>
-      </c>
-      <c r="DB2" s="17">
-        <v>-18.423999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P3" s="13">
-        <v>43948</v>
-      </c>
-      <c r="R3" s="2">
-        <v>2.7977782000000002</v>
-      </c>
-      <c r="S3">
-        <f t="shared" ref="S3:S23" si="0">R3/1000*60*60*24</f>
-        <v>241.72803648000001</v>
-      </c>
-      <c r="T3">
-        <f t="shared" ref="T3:T23" si="1">S3/1200000</f>
-        <v>2.014400304E-4</v>
-      </c>
-      <c r="U3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V3">
-        <f t="shared" ref="V3:V23" si="2">T3</f>
-        <v>2.014400304E-4</v>
-      </c>
-      <c r="W3" t="s">
-        <v>233</v>
-      </c>
-      <c r="X3" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y3" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z3" s="41">
-        <v>4.91</v>
-      </c>
-      <c r="AA3" s="41">
-        <v>30</v>
-      </c>
-      <c r="AB3" s="41">
-        <v>22.903300000000002</v>
-      </c>
-      <c r="AC3" s="41">
-        <v>96.99</v>
-      </c>
-      <c r="AD3" s="41">
-        <v>0.46860000000000002</v>
-      </c>
-      <c r="AE3" s="41">
-        <v>8.58</v>
-      </c>
-      <c r="AF3" s="41">
-        <v>2.72</v>
-      </c>
-      <c r="AG3" s="41">
-        <v>1205.71</v>
-      </c>
-      <c r="AP3" s="41">
-        <v>1095.5672999999999</v>
-      </c>
-      <c r="AR3" s="41">
-        <v>-13.3948</v>
-      </c>
-      <c r="AT3" s="42">
-        <v>0.77274029767522401</v>
-      </c>
-      <c r="AU3" s="42"/>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42">
-        <v>0.77</v>
-      </c>
-      <c r="BF3" s="47">
-        <f t="shared" ref="BF3:BF22" si="3">AW3</f>
-        <v>0.77</v>
-      </c>
-      <c r="BG3" s="47">
-        <f t="shared" ref="BG3:BG22" si="4">AT3</f>
-        <v>0.77274029767522401</v>
-      </c>
-      <c r="BH3" s="47">
-        <f t="shared" ref="BH3:BH22" si="5">Z3</f>
-        <v>4.91</v>
-      </c>
-      <c r="BJ3" s="47">
-        <f t="shared" ref="BJ3:BJ22" si="6">AB3</f>
-        <v>22.903300000000002</v>
-      </c>
-      <c r="BZ3" s="47">
-        <f t="shared" ref="BZ3:BZ23" si="7">AR3</f>
-        <v>-13.3948</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="CE3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="CF3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="CH3">
-        <v>2020</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>232</v>
-      </c>
-      <c r="CL3" s="3">
-        <v>104.86020000000001</v>
-      </c>
-      <c r="CM3" s="3">
-        <v>0.48080000000000001</v>
-      </c>
-      <c r="CN3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP3" s="5">
-        <v>14.7</v>
-      </c>
-      <c r="CQ3" s="5">
-        <v>-28.754999999999999</v>
-      </c>
-      <c r="CV3" s="9" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P4" s="13">
-        <v>44071</v>
-      </c>
-      <c r="R4">
-        <v>1.7957520000000001E-3</v>
-      </c>
-      <c r="S4">
+      <c r="X4" s="41">
+        <v>22.486699999999999</v>
+      </c>
+      <c r="Y4" s="41">
+        <v>14.82</v>
+      </c>
+      <c r="Z4" s="41">
+        <v>0.39989999999999998</v>
+      </c>
+      <c r="AA4" s="41">
+        <v>5.08</v>
+      </c>
+      <c r="AB4" s="41">
+        <v>4.8</v>
+      </c>
+      <c r="AC4" s="41">
+        <v>1416.32</v>
+      </c>
+      <c r="AL4" s="41">
+        <v>1550.1451999999999</v>
+      </c>
+      <c r="AN4" s="41">
+        <v>-12.764787</v>
+      </c>
+      <c r="AP4" s="42">
+        <v>0.99209155055100096</v>
+      </c>
+      <c r="AQ4" s="42">
+        <v>1169.9999855250701</v>
+      </c>
+      <c r="AR4" s="42">
+        <v>9.4814293486727692</v>
+      </c>
+      <c r="AS4" s="42">
+        <v>0.80060533553276503</v>
+      </c>
+      <c r="BB4" s="47">
         <f t="shared" si="0"/>
-        <v>0.15515297280000001</v>
-      </c>
-      <c r="T4">
+        <v>0.80060533553276503</v>
+      </c>
+      <c r="BC4" s="47">
         <f t="shared" si="1"/>
-        <v>1.2929414400000001E-7</v>
-      </c>
-      <c r="U4" t="s">
-        <v>3</v>
-      </c>
-      <c r="V4">
+        <v>0.99209155055100096</v>
+      </c>
+      <c r="BD4" s="47">
         <f t="shared" si="2"/>
-        <v>1.2929414400000001E-7</v>
-      </c>
-      <c r="W4" t="s">
-        <v>233</v>
-      </c>
-      <c r="X4" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y4" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z4" s="41">
         <v>5.86</v>
-      </c>
-      <c r="AA4" s="41">
-        <v>30</v>
-      </c>
-      <c r="AB4" s="41">
-        <v>22.486699999999999</v>
-      </c>
-      <c r="AC4" s="41">
-        <v>14.82</v>
-      </c>
-      <c r="AD4" s="41">
-        <v>0.39989999999999998</v>
-      </c>
-      <c r="AE4" s="41">
-        <v>5.08</v>
-      </c>
-      <c r="AF4" s="41">
-        <v>4.8</v>
-      </c>
-      <c r="AG4" s="41">
-        <v>1416.32</v>
-      </c>
-      <c r="AP4" s="41">
-        <v>1550.1451999999999</v>
-      </c>
-      <c r="AR4" s="41">
-        <v>-12.764787</v>
-      </c>
-      <c r="AT4" s="42">
-        <v>0.99209155055100096</v>
-      </c>
-      <c r="AU4" s="42">
-        <v>1169.9999855250701</v>
-      </c>
-      <c r="AV4" s="42">
-        <v>9.4814293486727692</v>
-      </c>
-      <c r="AW4" s="42">
-        <v>0.80060533553276503</v>
       </c>
       <c r="BF4" s="47">
         <f t="shared" si="3"/>
-        <v>0.80060533553276503</v>
-      </c>
-      <c r="BG4" s="47">
+        <v>22.486699999999999</v>
+      </c>
+      <c r="BV4" s="47">
         <f t="shared" si="4"/>
-        <v>0.99209155055100096</v>
-      </c>
-      <c r="BH4" s="47">
-        <f t="shared" si="5"/>
-        <v>5.86</v>
-      </c>
-      <c r="BJ4" s="47">
-        <f t="shared" si="6"/>
-        <v>22.486699999999999</v>
-      </c>
-      <c r="BZ4" s="47">
-        <f t="shared" si="7"/>
         <v>-12.764787</v>
       </c>
-      <c r="CD4" s="2" t="s">
+      <c r="BZ4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="CE4" s="1" t="s">
+      <c r="CA4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="CF4" s="1" t="s">
+      <c r="CB4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="CH4">
+      <c r="CC4">
+        <v>241</v>
+      </c>
+      <c r="CD4">
         <v>2020</v>
       </c>
-      <c r="CK4" t="s">
+      <c r="CG4" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH4" s="3">
+        <v>101.8592</v>
+      </c>
+      <c r="CI4" s="3">
+        <v>0.46820000000000001</v>
+      </c>
+      <c r="CJ4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL4" s="5">
+        <v>13.2</v>
+      </c>
+      <c r="CM4" s="5">
+        <v>-28.8</v>
+      </c>
+      <c r="CP4" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="CQ4" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="CR4" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS4" s="14">
+        <v>97.249799999999993</v>
+      </c>
+      <c r="CT4" s="15">
+        <v>0.42370000000000002</v>
+      </c>
+      <c r="CU4" s="16">
+        <v>224</v>
+      </c>
+      <c r="CV4" s="16">
+        <v>35</v>
+      </c>
+      <c r="CW4" s="15">
+        <v>3.04</v>
+      </c>
+      <c r="CX4" s="17">
+        <v>-18.231999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13">
+        <v>44125</v>
+      </c>
+      <c r="C5">
+        <v>-0.2</v>
+      </c>
+      <c r="D5">
+        <v>0.7</v>
+      </c>
+      <c r="E5">
+        <v>-1.8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>227</v>
+      </c>
+      <c r="G5">
+        <v>4.7</v>
+      </c>
+      <c r="H5">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I5">
+        <v>0.9</v>
+      </c>
+      <c r="J5">
+        <v>6.5</v>
+      </c>
+      <c r="K5" t="s">
+        <v>227</v>
+      </c>
+      <c r="L5">
+        <v>-0.9</v>
+      </c>
+      <c r="M5">
+        <v>3.9</v>
+      </c>
+      <c r="N5">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="O5" t="s">
+        <v>228</v>
+      </c>
+      <c r="P5" s="48">
+        <v>44125</v>
+      </c>
+      <c r="R5">
+        <v>0.705102278582596</v>
+      </c>
+      <c r="S5" t="s">
+        <v>3</v>
+      </c>
+      <c r="T5" t="s">
         <v>232</v>
       </c>
-      <c r="CL4" s="3">
-        <v>101.8592</v>
-      </c>
-      <c r="CM4" s="3">
-        <v>0.46820000000000001</v>
-      </c>
-      <c r="CN4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP4" s="5">
-        <v>13.2</v>
-      </c>
-      <c r="CQ4" s="5">
-        <v>-28.8</v>
-      </c>
-      <c r="CT4" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="CU4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="CV4" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW4" s="14">
-        <v>97.249799999999993</v>
-      </c>
-      <c r="CX4" s="15">
-        <v>0.42370000000000002</v>
-      </c>
-      <c r="CY4" s="16">
-        <v>224</v>
-      </c>
-      <c r="CZ4" s="16">
-        <v>35</v>
-      </c>
-      <c r="DA4" s="15">
-        <v>3.04</v>
-      </c>
-      <c r="DB4" s="17">
-        <v>-18.231999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P5" s="13">
-        <v>44125</v>
-      </c>
-      <c r="R5" s="2">
-        <v>0.98031077300000002</v>
-      </c>
-      <c r="S5">
+      <c r="U5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="V5" s="41">
+        <v>5.2</v>
+      </c>
+      <c r="W5" s="41">
+        <v>32</v>
+      </c>
+      <c r="X5" s="41">
+        <v>24</v>
+      </c>
+      <c r="Y5" s="41">
+        <v>43.99</v>
+      </c>
+      <c r="Z5" s="41">
+        <v>0.46</v>
+      </c>
+      <c r="AA5" s="41">
+        <v>12.92</v>
+      </c>
+      <c r="AB5" s="41">
+        <v>3.9</v>
+      </c>
+      <c r="AC5" s="41">
+        <v>1647.34</v>
+      </c>
+      <c r="AL5" s="41">
+        <v>1523.7797</v>
+      </c>
+      <c r="AN5" s="41">
+        <v>-13.025029</v>
+      </c>
+      <c r="AP5" s="42">
+        <v>0.69974502940305305</v>
+      </c>
+      <c r="AQ5" s="42">
+        <v>782.97814842027606</v>
+      </c>
+      <c r="AR5" s="42">
+        <v>3.4419002692160698</v>
+      </c>
+      <c r="AS5" s="42">
+        <v>0.66972073663818499</v>
+      </c>
+      <c r="BB5" s="47">
         <f t="shared" si="0"/>
-        <v>84.698850787200001</v>
-      </c>
-      <c r="T5">
+        <v>0.66972073663818499</v>
+      </c>
+      <c r="BC5" s="47">
         <f t="shared" si="1"/>
-        <v>7.0582375655999996E-5</v>
-      </c>
-      <c r="U5" t="s">
-        <v>3</v>
-      </c>
-      <c r="V5">
+        <v>0.69974502940305305</v>
+      </c>
+      <c r="BD5" s="47">
         <f t="shared" si="2"/>
-        <v>7.0582375655999996E-5</v>
-      </c>
-      <c r="W5" t="s">
-        <v>233</v>
-      </c>
-      <c r="X5" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y5" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z5" s="41">
         <v>5.2</v>
-      </c>
-      <c r="AA5" s="41">
-        <v>32</v>
-      </c>
-      <c r="AB5" s="41">
-        <v>24</v>
-      </c>
-      <c r="AC5" s="41">
-        <v>43.99</v>
-      </c>
-      <c r="AD5" s="41">
-        <v>0.46</v>
-      </c>
-      <c r="AE5" s="41">
-        <v>12.92</v>
-      </c>
-      <c r="AF5" s="41">
-        <v>3.9</v>
-      </c>
-      <c r="AG5" s="41">
-        <v>1647.34</v>
-      </c>
-      <c r="AP5" s="41">
-        <v>1523.7797</v>
-      </c>
-      <c r="AR5" s="41">
-        <v>-13.025029</v>
-      </c>
-      <c r="AT5" s="42">
-        <v>0.69974502940305305</v>
-      </c>
-      <c r="AU5" s="42">
-        <v>782.97814842027606</v>
-      </c>
-      <c r="AV5" s="42">
-        <v>3.4419002692160698</v>
-      </c>
-      <c r="AW5" s="42">
-        <v>0.66972073663818499</v>
       </c>
       <c r="BF5" s="47">
         <f t="shared" si="3"/>
-        <v>0.66972073663818499</v>
-      </c>
-      <c r="BG5" s="47">
+        <v>24</v>
+      </c>
+      <c r="BV5" s="47">
         <f t="shared" si="4"/>
-        <v>0.69974502940305305</v>
-      </c>
-      <c r="BH5" s="47">
-        <f t="shared" si="5"/>
-        <v>5.2</v>
-      </c>
-      <c r="BJ5" s="47">
-        <f t="shared" si="6"/>
-        <v>24</v>
-      </c>
-      <c r="BZ5" s="47">
-        <f t="shared" si="7"/>
         <v>-13.025029</v>
       </c>
-      <c r="CD5" s="2" t="s">
+      <c r="BZ5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="CE5" s="1" t="s">
+      <c r="CA5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="CF5" s="1" t="s">
+      <c r="CB5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="CH5">
+      <c r="CC5">
+        <v>295</v>
+      </c>
+      <c r="CD5">
         <v>2020</v>
       </c>
-      <c r="CK5" t="s">
+      <c r="CG5" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH5" s="3">
+        <v>103.7383</v>
+      </c>
+      <c r="CI5" s="3">
+        <v>0.48770000000000002</v>
+      </c>
+      <c r="CJ5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL5" s="3">
+        <v>11.45</v>
+      </c>
+      <c r="CM5" s="5">
+        <v>-28.152000000000001</v>
+      </c>
+      <c r="CR5" s="9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13">
+        <v>44315</v>
+      </c>
+      <c r="C6">
+        <v>0.8</v>
+      </c>
+      <c r="D6">
+        <v>5.5</v>
+      </c>
+      <c r="E6">
+        <v>-5.3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G6">
+        <v>0.8</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>17.3</v>
+      </c>
+      <c r="J6">
+        <v>3.8</v>
+      </c>
+      <c r="K6">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2.4</v>
+      </c>
+      <c r="N6">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="O6" t="s">
+        <v>228</v>
+      </c>
+      <c r="P6" s="48">
+        <v>44315</v>
+      </c>
+      <c r="R6">
+        <v>1.42652935508005</v>
+      </c>
+      <c r="S6" t="s">
+        <v>3</v>
+      </c>
+      <c r="T6" t="s">
         <v>232</v>
       </c>
-      <c r="CL5" s="3">
-        <v>103.7383</v>
-      </c>
-      <c r="CM5" s="3">
-        <v>0.48770000000000002</v>
-      </c>
-      <c r="CN5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP5" s="3">
-        <v>11.45</v>
-      </c>
-      <c r="CQ5" s="5">
-        <v>-28.152000000000001</v>
-      </c>
-      <c r="CV5" s="9" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="6" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P6" s="13">
-        <v>44315</v>
-      </c>
-      <c r="R6" s="2">
-        <v>1.9812636960000001</v>
-      </c>
-      <c r="S6">
+      <c r="U6" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="V6" s="34">
+        <v>5.05</v>
+      </c>
+      <c r="W6" s="34">
+        <v>24.7</v>
+      </c>
+      <c r="X6" s="34">
+        <v>20.7</v>
+      </c>
+      <c r="Y6" s="34">
+        <v>53.94</v>
+      </c>
+      <c r="Z6" s="34">
+        <v>0.39</v>
+      </c>
+      <c r="AA6" s="34">
+        <v>10.36</v>
+      </c>
+      <c r="AB6" s="34">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AC6" s="34">
+        <v>1131.46</v>
+      </c>
+      <c r="AL6" s="34">
+        <v>1081.1025</v>
+      </c>
+      <c r="AN6" s="34">
+        <v>-13.740912</v>
+      </c>
+      <c r="AP6" s="35">
+        <v>0.65993203565949998</v>
+      </c>
+      <c r="AQ6" s="35"/>
+      <c r="AR6" s="35"/>
+      <c r="AS6" s="35"/>
+      <c r="BB6" s="47">
         <f t="shared" si="0"/>
-        <v>171.1811833344</v>
-      </c>
-      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="47">
         <f t="shared" si="1"/>
-        <v>1.42650986112E-4</v>
-      </c>
-      <c r="U6" t="s">
-        <v>3</v>
-      </c>
-      <c r="V6">
+        <v>0.65993203565949998</v>
+      </c>
+      <c r="BD6" s="47">
         <f t="shared" si="2"/>
-        <v>1.42650986112E-4</v>
-      </c>
-      <c r="W6" t="s">
-        <v>233</v>
-      </c>
-      <c r="X6" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y6" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z6" s="34">
         <v>5.05</v>
       </c>
-      <c r="AA6" s="34">
-        <v>24.7</v>
-      </c>
-      <c r="AB6" s="34">
-        <v>20.7</v>
-      </c>
-      <c r="AC6" s="34">
-        <v>53.94</v>
-      </c>
-      <c r="AD6" s="34">
-        <v>0.39</v>
-      </c>
-      <c r="AE6" s="34">
-        <v>10.36</v>
-      </c>
-      <c r="AF6" s="34">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="AG6" s="34">
-        <v>1131.46</v>
-      </c>
-      <c r="AP6" s="34">
-        <v>1081.1025</v>
-      </c>
-      <c r="AR6" s="34">
-        <v>-13.740912</v>
-      </c>
-      <c r="AT6" s="35">
-        <v>0.65993203565949998</v>
-      </c>
-      <c r="AU6" s="35"/>
-      <c r="AV6" s="35"/>
-      <c r="AW6" s="35"/>
       <c r="BF6" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BG6" s="47">
+        <v>20.7</v>
+      </c>
+      <c r="BV6" s="47">
         <f t="shared" si="4"/>
-        <v>0.65993203565949998</v>
-      </c>
-      <c r="BH6" s="47">
-        <f t="shared" si="5"/>
-        <v>5.05</v>
-      </c>
-      <c r="BJ6" s="47">
-        <f t="shared" si="6"/>
-        <v>20.7</v>
-      </c>
-      <c r="BZ6" s="47">
-        <f t="shared" si="7"/>
         <v>-13.740912</v>
       </c>
-      <c r="CD6" s="2" t="s">
+      <c r="BZ6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="CE6" s="1" t="s">
+      <c r="CA6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="CF6" s="1" t="s">
+      <c r="CB6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="CH6">
+      <c r="CC6">
+        <v>119</v>
+      </c>
+      <c r="CD6">
         <v>2021</v>
       </c>
-      <c r="CK6" t="s">
+      <c r="CG6" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH6" s="3">
+        <v>104.694</v>
+      </c>
+      <c r="CI6" s="3">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="CJ6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL6" s="3">
+        <v>14.8</v>
+      </c>
+      <c r="CM6" s="5">
+        <v>-28.32</v>
+      </c>
+      <c r="CP6" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="CQ6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="CR6" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS6" s="14">
+        <v>98.632499999999993</v>
+      </c>
+      <c r="CT6" s="15">
+        <v>0.46610000000000001</v>
+      </c>
+      <c r="CU6" s="16">
+        <v>111</v>
+      </c>
+      <c r="CV6" s="16">
+        <v>38</v>
+      </c>
+      <c r="CW6" s="15">
+        <v>2.95</v>
+      </c>
+      <c r="CX6" s="17">
+        <v>-16.097000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13">
+        <v>44427</v>
+      </c>
+      <c r="C7">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>16.2</v>
+      </c>
+      <c r="E7">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F7" t="s">
+        <v>227</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>3.4</v>
+      </c>
+      <c r="I7">
+        <v>9.5</v>
+      </c>
+      <c r="J7">
+        <v>13.2</v>
+      </c>
+      <c r="K7">
+        <v>23.2</v>
+      </c>
+      <c r="L7">
+        <v>3.5</v>
+      </c>
+      <c r="M7">
+        <v>1.3</v>
+      </c>
+      <c r="N7">
+        <v>5.6</v>
+      </c>
+      <c r="O7" t="s">
+        <v>228</v>
+      </c>
+      <c r="P7" s="48">
+        <v>44427</v>
+      </c>
+      <c r="R7">
+        <v>1.50187150171214</v>
+      </c>
+      <c r="S7" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" t="s">
         <v>232</v>
-      </c>
-      <c r="CL6" s="3">
-        <v>104.694</v>
-      </c>
-      <c r="CM6" s="3">
-        <v>0.47899999999999998</v>
-      </c>
-      <c r="CN6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP6" s="3">
-        <v>14.8</v>
-      </c>
-      <c r="CQ6" s="5">
-        <v>-28.32</v>
-      </c>
-      <c r="CT6" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="CU6" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="CV6" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW6" s="14">
-        <v>98.632499999999993</v>
-      </c>
-      <c r="CX6" s="15">
-        <v>0.46610000000000001</v>
-      </c>
-      <c r="CY6" s="16">
-        <v>111</v>
-      </c>
-      <c r="CZ6" s="16">
-        <v>38</v>
-      </c>
-      <c r="DA6" s="15">
-        <v>2.95</v>
-      </c>
-      <c r="DB6" s="17">
-        <v>-16.097000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P7" s="13">
-        <v>44427</v>
-      </c>
-      <c r="R7" s="2">
-        <v>2.0836396480000001</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="0"/>
-        <v>180.02646558719999</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="1"/>
-        <v>1.50022054656E-4</v>
       </c>
       <c r="U7" t="s">
         <v>3</v>
       </c>
       <c r="V7">
+        <v>5.51</v>
+      </c>
+      <c r="W7">
+        <v>29.435000000000002</v>
+      </c>
+      <c r="X7">
+        <v>25.35</v>
+      </c>
+      <c r="Y7">
+        <v>21.355</v>
+      </c>
+      <c r="Z7">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="AA7">
+        <v>15.215</v>
+      </c>
+      <c r="AB7">
+        <v>5.5600000000000005</v>
+      </c>
+      <c r="AC7">
+        <v>1226.2049999999999</v>
+      </c>
+      <c r="AL7">
+        <v>1461.92615</v>
+      </c>
+      <c r="AN7">
+        <v>-13.069607000000001</v>
+      </c>
+      <c r="AP7">
+        <v>0.72969560963047941</v>
+      </c>
+      <c r="AR7">
+        <v>13.89030579397286</v>
+      </c>
+      <c r="AS7">
+        <f>AP7</f>
+        <v>0.72969560963047941</v>
+      </c>
+      <c r="BB7" s="47">
+        <f t="shared" si="0"/>
+        <v>0.72969560963047941</v>
+      </c>
+      <c r="BC7" s="47">
+        <f t="shared" si="1"/>
+        <v>0.72969560963047941</v>
+      </c>
+      <c r="BD7" s="47">
         <f t="shared" si="2"/>
-        <v>1.50022054656E-4</v>
-      </c>
-      <c r="W7" t="s">
-        <v>233</v>
-      </c>
-      <c r="X7" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z7">
         <v>5.51</v>
-      </c>
-      <c r="AA7">
-        <v>29.435000000000002</v>
-      </c>
-      <c r="AB7">
-        <v>25.35</v>
-      </c>
-      <c r="AC7">
-        <v>21.355</v>
-      </c>
-      <c r="AD7">
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="AE7">
-        <v>15.215</v>
-      </c>
-      <c r="AF7">
-        <v>5.5600000000000005</v>
-      </c>
-      <c r="AG7">
-        <v>1226.2049999999999</v>
-      </c>
-      <c r="AP7">
-        <v>1461.92615</v>
-      </c>
-      <c r="AR7">
-        <v>-13.069607000000001</v>
-      </c>
-      <c r="AT7">
-        <v>0.72969560963047941</v>
-      </c>
-      <c r="AV7">
-        <v>13.89030579397286</v>
-      </c>
-      <c r="AW7">
-        <f>AT7</f>
-        <v>0.72969560963047941</v>
       </c>
       <c r="BF7" s="47">
         <f t="shared" si="3"/>
-        <v>0.72969560963047941</v>
-      </c>
-      <c r="BG7" s="47">
+        <v>25.35</v>
+      </c>
+      <c r="BV7" s="47">
         <f t="shared" si="4"/>
-        <v>0.72969560963047941</v>
-      </c>
-      <c r="BH7" s="47">
-        <f t="shared" si="5"/>
-        <v>5.51</v>
-      </c>
-      <c r="BJ7" s="47">
-        <f t="shared" si="6"/>
-        <v>25.35</v>
-      </c>
-      <c r="BZ7" s="47">
-        <f t="shared" si="7"/>
         <v>-13.069607000000001</v>
       </c>
-      <c r="CD7" s="2" t="s">
+      <c r="BZ7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="CE7" s="1" t="s">
+      <c r="CA7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="CF7" s="1" t="s">
+      <c r="CB7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="CH7">
+      <c r="CC7">
+        <v>231</v>
+      </c>
+      <c r="CD7">
         <v>2021</v>
       </c>
-      <c r="CK7" t="s">
+      <c r="CG7" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH7" s="3">
+        <v>104.6589</v>
+      </c>
+      <c r="CI7" s="3">
+        <v>0.47889999999999999</v>
+      </c>
+      <c r="CJ7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL7" s="3">
+        <v>36.04</v>
+      </c>
+      <c r="CM7" s="5">
+        <v>-28.779</v>
+      </c>
+      <c r="CP7" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="CQ7" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="CR7" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS7" s="14">
+        <v>99.498000000000005</v>
+      </c>
+      <c r="CT7" s="15">
+        <v>0.4577</v>
+      </c>
+      <c r="CU7" s="16">
+        <v>40</v>
+      </c>
+      <c r="CV7" s="16">
+        <v>37</v>
+      </c>
+      <c r="CW7" s="15">
+        <v>2.52</v>
+      </c>
+      <c r="CX7" s="17">
+        <v>-17.045000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13">
+        <v>44464</v>
+      </c>
+      <c r="C8">
+        <v>5.4</v>
+      </c>
+      <c r="D8">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>227</v>
+      </c>
+      <c r="G8">
+        <v>7.8</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>3.6</v>
+      </c>
+      <c r="J8">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="K8">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="L8">
+        <v>-0.4</v>
+      </c>
+      <c r="M8">
+        <v>2.5</v>
+      </c>
+      <c r="N8">
+        <v>10.7</v>
+      </c>
+      <c r="O8" t="s">
+        <v>228</v>
+      </c>
+      <c r="P8" s="48">
+        <v>44464</v>
+      </c>
+      <c r="R8">
+        <v>3.4877404926156998</v>
+      </c>
+      <c r="S8" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" t="s">
         <v>232</v>
       </c>
-      <c r="CL7" s="3">
-        <v>104.6589</v>
-      </c>
-      <c r="CM7" s="3">
-        <v>0.47889999999999999</v>
-      </c>
-      <c r="CN7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP7" s="3">
-        <v>36.04</v>
-      </c>
-      <c r="CQ7" s="5">
-        <v>-28.779</v>
-      </c>
-      <c r="CT7" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="CU7" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="CV7" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW7" s="14">
-        <v>99.498000000000005</v>
-      </c>
-      <c r="CX7" s="15">
-        <v>0.4577</v>
-      </c>
-      <c r="CY7" s="16">
-        <v>40</v>
-      </c>
-      <c r="CZ7" s="16">
-        <v>37</v>
-      </c>
-      <c r="DA7" s="15">
-        <v>2.52</v>
-      </c>
-      <c r="DB7" s="17">
-        <v>-17.045000000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P8" s="13">
-        <v>44493</v>
-      </c>
-      <c r="R8" s="2">
-        <v>4.8347428949999998</v>
-      </c>
-      <c r="S8">
+      <c r="U8" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="41">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="W8" s="41">
+        <v>30.52</v>
+      </c>
+      <c r="X8" s="41">
+        <v>31.8</v>
+      </c>
+      <c r="Y8" s="41">
+        <v>26.84</v>
+      </c>
+      <c r="Z8" s="41">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AA8" s="41">
+        <v>12.56</v>
+      </c>
+      <c r="AB8" s="41">
+        <v>4.55</v>
+      </c>
+      <c r="AC8" s="41">
+        <v>1142.58</v>
+      </c>
+      <c r="AL8" s="41">
+        <v>1948.68</v>
+      </c>
+      <c r="AN8" s="41">
+        <v>-12.69239</v>
+      </c>
+      <c r="AP8" s="42">
+        <v>0.58288602667799105</v>
+      </c>
+      <c r="AQ8" s="42"/>
+      <c r="AR8" s="42">
+        <v>2.6060490454418699</v>
+      </c>
+      <c r="AS8" s="42">
+        <f>AP8</f>
+        <v>0.58288602667799105</v>
+      </c>
+      <c r="BB8" s="47">
         <f t="shared" si="0"/>
-        <v>417.72178612800008</v>
-      </c>
-      <c r="T8">
+        <v>0.58288602667799105</v>
+      </c>
+      <c r="BC8" s="47">
         <f t="shared" si="1"/>
-        <v>3.4810148844000005E-4</v>
-      </c>
-      <c r="U8" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8">
+        <v>0.58288602667799105</v>
+      </c>
+      <c r="BD8" s="47">
         <f t="shared" si="2"/>
-        <v>3.4810148844000005E-4</v>
-      </c>
-      <c r="W8" t="s">
-        <v>233</v>
-      </c>
-      <c r="X8" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y8" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="41">
         <v>4.9000000000000004</v>
-      </c>
-      <c r="AA8" s="41">
-        <v>30.52</v>
-      </c>
-      <c r="AB8" s="41">
-        <v>31.8</v>
-      </c>
-      <c r="AC8" s="41">
-        <v>26.84</v>
-      </c>
-      <c r="AD8" s="41">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AE8" s="41">
-        <v>12.56</v>
-      </c>
-      <c r="AF8" s="41">
-        <v>4.55</v>
-      </c>
-      <c r="AG8" s="41">
-        <v>1142.58</v>
-      </c>
-      <c r="AP8" s="41">
-        <v>1948.68</v>
-      </c>
-      <c r="AR8" s="41">
-        <v>-12.69239</v>
-      </c>
-      <c r="AT8" s="42">
-        <v>0.58288602667799105</v>
-      </c>
-      <c r="AU8" s="42"/>
-      <c r="AV8" s="42">
-        <v>2.6060490454418699</v>
-      </c>
-      <c r="AW8" s="42">
-        <f>AT8</f>
-        <v>0.58288602667799105</v>
       </c>
       <c r="BF8" s="47">
         <f t="shared" si="3"/>
-        <v>0.58288602667799105</v>
-      </c>
-      <c r="BG8" s="47">
+        <v>31.8</v>
+      </c>
+      <c r="BV8" s="47">
         <f t="shared" si="4"/>
-        <v>0.58288602667799105</v>
-      </c>
-      <c r="BH8" s="47">
-        <f t="shared" si="5"/>
+        <v>-12.69239</v>
+      </c>
+      <c r="BZ8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="CA8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="CB8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="CC8">
+        <v>268</v>
+      </c>
+      <c r="CD8">
+        <v>2021</v>
+      </c>
+      <c r="CG8" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH8" s="3">
+        <v>106.10429999999999</v>
+      </c>
+      <c r="CI8" s="3">
+        <v>0.53580000000000005</v>
+      </c>
+      <c r="CJ8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL8" s="5">
+        <v>33.21</v>
+      </c>
+      <c r="CM8" s="5">
+        <v>-28.42</v>
+      </c>
+      <c r="CP8" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="CQ8" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="CR8" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS8" s="14">
+        <v>109.7132</v>
+      </c>
+      <c r="CT8" s="15">
+        <v>0.50549999999999995</v>
+      </c>
+      <c r="CU8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW8" s="15">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="CX8" s="17">
+        <v>-16.55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13">
+        <v>44493</v>
+      </c>
+      <c r="C9">
+        <v>-3.3</v>
+      </c>
+      <c r="D9">
+        <v>1.8</v>
+      </c>
+      <c r="E9">
+        <v>-10.5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H9">
+        <v>3.6</v>
+      </c>
+      <c r="I9">
+        <v>0.6</v>
+      </c>
+      <c r="J9">
         <v>4.9000000000000004</v>
       </c>
-      <c r="BJ8" s="47">
-        <f t="shared" si="6"/>
-        <v>31.8</v>
-      </c>
-      <c r="BZ8" s="47">
-        <f t="shared" si="7"/>
-        <v>-12.69239</v>
-      </c>
-      <c r="CD8" s="2" t="s">
+      <c r="K9" t="s">
+        <v>227</v>
+      </c>
+      <c r="L9" t="s">
+        <v>227</v>
+      </c>
+      <c r="M9">
+        <v>1.7</v>
+      </c>
+      <c r="N9">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O9" t="s">
+        <v>228</v>
+      </c>
+      <c r="P9" s="48">
+        <v>44493</v>
+      </c>
+      <c r="R9">
+        <v>1.7893817847507101</v>
+      </c>
+      <c r="S9" t="s">
         <v>3</v>
       </c>
-      <c r="CE8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="CF8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="CH8">
-        <v>2021</v>
-      </c>
-      <c r="CK8" t="s">
+      <c r="T9" t="s">
         <v>232</v>
       </c>
-      <c r="CL8" s="3">
-        <v>106.10429999999999</v>
-      </c>
-      <c r="CM8" s="3">
-        <v>0.53580000000000005</v>
-      </c>
-      <c r="CN8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP8" s="5">
-        <v>33.21</v>
-      </c>
-      <c r="CQ8" s="5">
-        <v>-28.42</v>
-      </c>
-      <c r="CT8" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="CU8" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="CV8" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW8" s="14">
-        <v>109.7132</v>
-      </c>
-      <c r="CX8" s="15">
-        <v>0.50549999999999995</v>
-      </c>
-      <c r="CY8" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="CZ8" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="DA8" s="15">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="DB8" s="17">
-        <v>-16.55</v>
-      </c>
-    </row>
-    <row r="9" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P9" s="13">
-        <v>44684</v>
-      </c>
-      <c r="R9" s="2">
-        <v>2.4860604880000001</v>
-      </c>
-      <c r="S9">
+      <c r="U9" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="34">
+        <v>4.83</v>
+      </c>
+      <c r="W9" s="34">
+        <v>26.75</v>
+      </c>
+      <c r="X9" s="34">
+        <v>28.5</v>
+      </c>
+      <c r="Y9" s="34">
+        <v>25.99</v>
+      </c>
+      <c r="Z9" s="34">
+        <v>0.48</v>
+      </c>
+      <c r="AA9" s="34">
+        <v>11.52</v>
+      </c>
+      <c r="AB9" s="34">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="AC9" s="34">
+        <v>953.19200000000001</v>
+      </c>
+      <c r="AL9" s="34">
+        <v>1569.4863</v>
+      </c>
+      <c r="AN9" s="34">
+        <v>-13.039296999999999</v>
+      </c>
+      <c r="AP9" s="35">
+        <v>0.63855058284324795</v>
+      </c>
+      <c r="AQ9" s="35"/>
+      <c r="AR9" s="35">
+        <v>1.6486903427736499</v>
+      </c>
+      <c r="AS9" s="35">
+        <f>AP9</f>
+        <v>0.63855058284324795</v>
+      </c>
+      <c r="BB9" s="47">
         <f t="shared" si="0"/>
-        <v>214.79562616320004</v>
-      </c>
-      <c r="T9">
+        <v>0.63855058284324795</v>
+      </c>
+      <c r="BC9" s="47">
         <f t="shared" si="1"/>
-        <v>1.7899635513600004E-4</v>
-      </c>
-      <c r="U9" t="s">
-        <v>3</v>
-      </c>
-      <c r="V9">
+        <v>0.63855058284324795</v>
+      </c>
+      <c r="BD9" s="47">
         <f t="shared" si="2"/>
-        <v>1.7899635513600004E-4</v>
-      </c>
-      <c r="W9" t="s">
-        <v>233</v>
-      </c>
-      <c r="X9" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y9" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z9" s="34">
         <v>4.83</v>
-      </c>
-      <c r="AA9" s="34">
-        <v>26.75</v>
-      </c>
-      <c r="AB9" s="34">
-        <v>28.5</v>
-      </c>
-      <c r="AC9" s="34">
-        <v>25.99</v>
-      </c>
-      <c r="AD9" s="34">
-        <v>0.48</v>
-      </c>
-      <c r="AE9" s="34">
-        <v>11.52</v>
-      </c>
-      <c r="AF9" s="34">
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="AG9" s="34">
-        <v>953.19200000000001</v>
-      </c>
-      <c r="AP9" s="34">
-        <v>1569.4863</v>
-      </c>
-      <c r="AR9" s="34">
-        <v>-13.039296999999999</v>
-      </c>
-      <c r="AT9" s="35">
-        <v>0.63855058284324795</v>
-      </c>
-      <c r="AU9" s="35"/>
-      <c r="AV9" s="35">
-        <v>1.6486903427736499</v>
-      </c>
-      <c r="AW9" s="35">
-        <f>AT9</f>
-        <v>0.63855058284324795</v>
       </c>
       <c r="BF9" s="47">
         <f t="shared" si="3"/>
-        <v>0.63855058284324795</v>
-      </c>
-      <c r="BG9" s="47">
+        <v>28.5</v>
+      </c>
+      <c r="BV9" s="47">
         <f t="shared" si="4"/>
-        <v>0.63855058284324795</v>
-      </c>
-      <c r="BH9" s="47">
-        <f t="shared" si="5"/>
-        <v>4.83</v>
-      </c>
-      <c r="BJ9" s="47">
-        <f t="shared" si="6"/>
-        <v>28.5</v>
-      </c>
-      <c r="BZ9" s="47">
-        <f t="shared" si="7"/>
         <v>-13.039296999999999</v>
       </c>
-      <c r="CD9" s="2" t="s">
+      <c r="BZ9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="CE9" s="1" t="s">
+      <c r="CA9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="CF9" s="1" t="s">
+      <c r="CB9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="CH9">
+      <c r="CC9">
+        <v>297</v>
+      </c>
+      <c r="CD9">
         <v>2021</v>
       </c>
-      <c r="CK9" t="s">
+      <c r="CG9" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH9" s="3">
+        <v>104.49039999999999</v>
+      </c>
+      <c r="CI9" s="3">
+        <v>0.48139999999999999</v>
+      </c>
+      <c r="CJ9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL9" s="3">
+        <v>22.15</v>
+      </c>
+      <c r="CM9" s="5">
+        <v>-27.984999999999999</v>
+      </c>
+      <c r="CP9" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="CQ9" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="CR9" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS9" s="14">
+        <v>101.2383</v>
+      </c>
+      <c r="CT9" s="15">
+        <v>0.48170000000000002</v>
+      </c>
+      <c r="CU9" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV9" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW9" s="15">
+        <v>1.55</v>
+      </c>
+      <c r="CX9" s="17">
+        <v>-17.321999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13">
+        <v>44684</v>
+      </c>
+      <c r="C10">
+        <v>1.7</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>-6.9</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>-0.5</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>227</v>
+      </c>
+      <c r="J10">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="s">
+        <v>227</v>
+      </c>
+      <c r="L10" t="s">
+        <v>227</v>
+      </c>
+      <c r="M10">
+        <v>2.8</v>
+      </c>
+      <c r="N10">
+        <v>11.2</v>
+      </c>
+      <c r="O10" t="s">
+        <v>229</v>
+      </c>
+      <c r="P10" s="48">
+        <v>44684</v>
+      </c>
+      <c r="R10">
+        <v>2.3396154634610702</v>
+      </c>
+      <c r="S10" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" t="s">
         <v>232</v>
       </c>
-      <c r="CL9" s="3">
-        <v>104.49039999999999</v>
-      </c>
-      <c r="CM9" s="3">
-        <v>0.48139999999999999</v>
-      </c>
-      <c r="CN9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP9" s="3">
-        <v>22.15</v>
-      </c>
-      <c r="CQ9" s="5">
-        <v>-27.984999999999999</v>
-      </c>
-      <c r="CT9" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="CU9" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="CV9" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW9" s="14">
-        <v>101.2383</v>
-      </c>
-      <c r="CX9" s="15">
-        <v>0.48170000000000002</v>
-      </c>
-      <c r="CY9" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="CZ9" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="DA9" s="15">
-        <v>1.55</v>
-      </c>
-      <c r="DB9" s="17">
-        <v>-17.321999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P10" s="13">
-        <v>44858</v>
-      </c>
-      <c r="R10" s="2">
-        <v>3.2466057350000002</v>
-      </c>
-      <c r="S10">
+      <c r="U10" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="34">
+        <v>5.07</v>
+      </c>
+      <c r="W10" s="34">
+        <v>21.68</v>
+      </c>
+      <c r="X10" s="34">
+        <v>22.1</v>
+      </c>
+      <c r="Y10" s="34">
+        <v>58.83</v>
+      </c>
+      <c r="Z10" s="34">
+        <v>0.43</v>
+      </c>
+      <c r="AA10" s="34">
+        <v>12.85</v>
+      </c>
+      <c r="AB10" s="34">
+        <v>3.22</v>
+      </c>
+      <c r="AC10" s="34">
+        <v>898.61300000000006</v>
+      </c>
+      <c r="AL10" s="34">
+        <v>1700</v>
+      </c>
+      <c r="AN10" s="34">
+        <v>-13.745710000000001</v>
+      </c>
+      <c r="AP10" s="35">
+        <v>0.62791801140371495</v>
+      </c>
+      <c r="AQ10" s="35">
+        <v>711.16017255870395</v>
+      </c>
+      <c r="AR10" s="35"/>
+      <c r="AS10" s="35">
+        <v>0.62784841264659697</v>
+      </c>
+      <c r="BB10" s="47">
         <f t="shared" si="0"/>
-        <v>280.50673550400001</v>
-      </c>
-      <c r="T10">
+        <v>0.62784841264659697</v>
+      </c>
+      <c r="BC10" s="47">
         <f t="shared" si="1"/>
-        <v>2.3375561292000001E-4</v>
-      </c>
-      <c r="U10" t="s">
-        <v>3</v>
-      </c>
-      <c r="V10">
+        <v>0.62791801140371495</v>
+      </c>
+      <c r="BD10" s="47">
         <f t="shared" si="2"/>
-        <v>2.3375561292000001E-4</v>
-      </c>
-      <c r="W10" t="s">
-        <v>233</v>
-      </c>
-      <c r="X10" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y10" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z10" s="34">
         <v>5.07</v>
-      </c>
-      <c r="AA10" s="34">
-        <v>21.68</v>
-      </c>
-      <c r="AB10" s="34">
-        <v>22.1</v>
-      </c>
-      <c r="AC10" s="34">
-        <v>58.83</v>
-      </c>
-      <c r="AD10" s="34">
-        <v>0.43</v>
-      </c>
-      <c r="AE10" s="34">
-        <v>12.85</v>
-      </c>
-      <c r="AF10" s="34">
-        <v>3.22</v>
-      </c>
-      <c r="AG10" s="34">
-        <v>898.61300000000006</v>
-      </c>
-      <c r="AP10" s="34">
-        <v>1700</v>
-      </c>
-      <c r="AR10" s="34">
-        <v>-13.745710000000001</v>
-      </c>
-      <c r="AT10" s="35">
-        <v>0.62791801140371495</v>
-      </c>
-      <c r="AU10" s="35">
-        <v>711.16017255870395</v>
-      </c>
-      <c r="AV10" s="35"/>
-      <c r="AW10" s="35">
-        <v>0.62784841264659697</v>
       </c>
       <c r="BF10" s="47">
         <f t="shared" si="3"/>
-        <v>0.62784841264659697</v>
-      </c>
-      <c r="BG10" s="47">
+        <v>22.1</v>
+      </c>
+      <c r="BV10" s="47">
         <f t="shared" si="4"/>
-        <v>0.62791801140371495</v>
-      </c>
-      <c r="BH10" s="47">
-        <f t="shared" si="5"/>
-        <v>5.07</v>
-      </c>
-      <c r="BJ10" s="47">
-        <f t="shared" si="6"/>
-        <v>22.1</v>
-      </c>
-      <c r="BZ10" s="47">
-        <f t="shared" si="7"/>
         <v>-13.745710000000001</v>
       </c>
-      <c r="CD10" s="2" t="s">
+      <c r="BZ10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="CE10" s="1" t="s">
+      <c r="CA10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="CF10" s="1" t="s">
+      <c r="CB10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="CH10">
+      <c r="CC10">
+        <v>123</v>
+      </c>
+      <c r="CD10">
         <v>2022</v>
       </c>
-      <c r="CK10" t="s">
+      <c r="CG10" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH10" s="3">
+        <v>106.0802</v>
+      </c>
+      <c r="CI10" s="3">
+        <v>0.50419999999999998</v>
+      </c>
+      <c r="CJ10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL10" s="3">
+        <v>17.38</v>
+      </c>
+      <c r="CM10" s="5">
+        <v>-28.428000000000001</v>
+      </c>
+      <c r="CP10" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="CQ10" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="CR10" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS10" s="14">
+        <v>96.9084</v>
+      </c>
+      <c r="CT10" s="15">
+        <v>0.45369999999999999</v>
+      </c>
+      <c r="CU10" s="16">
+        <v>252</v>
+      </c>
+      <c r="CV10" s="16">
+        <v>38</v>
+      </c>
+      <c r="CW10" s="15">
+        <v>1.33</v>
+      </c>
+      <c r="CX10" s="17">
+        <v>-15.984</v>
+      </c>
+    </row>
+    <row r="11" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13">
+        <v>44796</v>
+      </c>
+      <c r="C11">
+        <v>11.4</v>
+      </c>
+      <c r="D11">
+        <v>20.9</v>
+      </c>
+      <c r="E11">
+        <v>0.9</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>13.4</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11" t="s">
+        <v>227</v>
+      </c>
+      <c r="L11" t="s">
+        <v>227</v>
+      </c>
+      <c r="M11">
+        <v>0.7</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11" t="s">
+        <v>229</v>
+      </c>
+      <c r="P11" s="48">
+        <v>44796</v>
+      </c>
+      <c r="R11">
+        <v>0.20586654312220601</v>
+      </c>
+      <c r="S11" t="s">
+        <v>3</v>
+      </c>
+      <c r="T11" t="s">
         <v>232</v>
       </c>
-      <c r="CL10" s="3">
-        <v>106.0802</v>
-      </c>
-      <c r="CM10" s="3">
-        <v>0.50419999999999998</v>
-      </c>
-      <c r="CN10" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO10" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP10" s="3">
-        <v>17.38</v>
-      </c>
-      <c r="CQ10" s="5">
-        <v>-28.428000000000001</v>
-      </c>
-      <c r="CT10" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="CU10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="CV10" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW10" s="14">
-        <v>96.9084</v>
-      </c>
-      <c r="CX10" s="15">
-        <v>0.45369999999999999</v>
-      </c>
-      <c r="CY10" s="16">
-        <v>252</v>
-      </c>
-      <c r="CZ10" s="16">
-        <v>38</v>
-      </c>
-      <c r="DA10" s="15">
-        <v>1.33</v>
-      </c>
-      <c r="DB10" s="17">
-        <v>-15.984</v>
-      </c>
-    </row>
-    <row r="11" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P11" s="13">
-        <v>44796</v>
-      </c>
-      <c r="R11" s="2">
-        <v>0.28571106600000001</v>
-      </c>
-      <c r="S11">
+      <c r="U11" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="V11" s="41">
+        <v>5.7799999999999994</v>
+      </c>
+      <c r="W11" s="41">
+        <v>26.9</v>
+      </c>
+      <c r="X11" s="41">
+        <v>20.9</v>
+      </c>
+      <c r="Y11" s="41">
+        <v>28.67</v>
+      </c>
+      <c r="Z11" s="41">
+        <v>0.4</v>
+      </c>
+      <c r="AA11" s="41">
+        <v>18.765000000000001</v>
+      </c>
+      <c r="AB11" s="41">
+        <v>2.83</v>
+      </c>
+      <c r="AC11" s="41">
+        <v>1128.9949999999999</v>
+      </c>
+      <c r="AL11" s="41">
+        <v>1450</v>
+      </c>
+      <c r="AN11" s="41">
+        <v>-13.042541</v>
+      </c>
+      <c r="AP11" s="41">
+        <v>0.79067267991136703</v>
+      </c>
+      <c r="AQ11" s="41">
+        <v>1303.0335319723099</v>
+      </c>
+      <c r="AR11" s="41">
+        <v>14.225639528177199</v>
+      </c>
+      <c r="AS11" s="41">
+        <v>0.86932337618368205</v>
+      </c>
+      <c r="BB11" s="47">
         <f t="shared" si="0"/>
-        <v>24.685436102400001</v>
-      </c>
-      <c r="T11">
+        <v>0.86932337618368205</v>
+      </c>
+      <c r="BC11" s="47">
         <f t="shared" si="1"/>
-        <v>2.0571196752000001E-5</v>
-      </c>
-      <c r="U11" t="s">
-        <v>3</v>
-      </c>
-      <c r="V11">
+        <v>0.79067267991136703</v>
+      </c>
+      <c r="BD11" s="47">
         <f t="shared" si="2"/>
-        <v>2.0571196752000001E-5</v>
-      </c>
-      <c r="W11" t="s">
-        <v>233</v>
-      </c>
-      <c r="X11" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y11" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z11" s="41">
         <v>5.7799999999999994</v>
-      </c>
-      <c r="AA11" s="41">
-        <v>26.9</v>
-      </c>
-      <c r="AB11" s="41">
-        <v>20.9</v>
-      </c>
-      <c r="AC11" s="41">
-        <v>28.67</v>
-      </c>
-      <c r="AD11" s="41">
-        <v>0.4</v>
-      </c>
-      <c r="AE11" s="41">
-        <v>18.765000000000001</v>
-      </c>
-      <c r="AF11" s="41">
-        <v>2.83</v>
-      </c>
-      <c r="AG11" s="41">
-        <v>1128.9949999999999</v>
-      </c>
-      <c r="AP11" s="41">
-        <v>1450</v>
-      </c>
-      <c r="AR11" s="41">
-        <v>-13.042541</v>
-      </c>
-      <c r="AT11" s="41">
-        <v>0.79067267991136703</v>
-      </c>
-      <c r="AU11" s="41">
-        <v>1303.0335319723099</v>
-      </c>
-      <c r="AV11" s="41">
-        <v>14.225639528177199</v>
-      </c>
-      <c r="AW11" s="41">
-        <v>0.86932337618368205</v>
       </c>
       <c r="BF11" s="47">
         <f t="shared" si="3"/>
-        <v>0.86932337618368205</v>
-      </c>
-      <c r="BG11" s="47">
+        <v>20.9</v>
+      </c>
+      <c r="BV11" s="47">
         <f t="shared" si="4"/>
-        <v>0.79067267991136703</v>
-      </c>
-      <c r="BH11" s="47">
-        <f t="shared" si="5"/>
-        <v>5.7799999999999994</v>
-      </c>
-      <c r="BJ11" s="47">
-        <f t="shared" si="6"/>
-        <v>20.9</v>
-      </c>
-      <c r="BZ11" s="47">
-        <f t="shared" si="7"/>
         <v>-13.042541</v>
       </c>
-      <c r="CD11" s="2" t="s">
+      <c r="BZ11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="CE11" s="1" t="s">
+      <c r="CA11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="CF11" s="1" t="s">
+      <c r="CB11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="CH11">
+      <c r="CC11">
+        <v>235</v>
+      </c>
+      <c r="CD11">
         <v>2022</v>
       </c>
-      <c r="CK11" t="s">
+      <c r="CG11" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH11" s="7">
+        <v>104.2628</v>
+      </c>
+      <c r="CI11" s="7">
+        <v>0.45450000000000002</v>
+      </c>
+      <c r="CJ11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL11" s="7">
+        <v>24.1</v>
+      </c>
+      <c r="CM11" s="7">
+        <v>-28.119</v>
+      </c>
+      <c r="CP11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="CQ11" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="CR11" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS11" s="15">
+        <v>99.284899999999993</v>
+      </c>
+      <c r="CT11" s="15">
+        <v>0.45579999999999998</v>
+      </c>
+      <c r="CU11" s="16">
+        <v>58</v>
+      </c>
+      <c r="CV11" s="16">
+        <v>37</v>
+      </c>
+      <c r="CW11" s="15">
+        <v>3.82</v>
+      </c>
+      <c r="CX11" s="17">
+        <v>-18.472999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13">
+        <v>44858</v>
+      </c>
+      <c r="C12">
+        <v>-3.5</v>
+      </c>
+      <c r="D12">
+        <v>0.4</v>
+      </c>
+      <c r="E12">
+        <v>-9.4</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1.4</v>
+      </c>
+      <c r="H12">
+        <v>0.4</v>
+      </c>
+      <c r="I12" t="s">
+        <v>227</v>
+      </c>
+      <c r="J12">
+        <v>4.2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>227</v>
+      </c>
+      <c r="L12" t="s">
+        <v>227</v>
+      </c>
+      <c r="M12">
+        <v>0.3</v>
+      </c>
+      <c r="N12">
+        <v>2.5</v>
+      </c>
+      <c r="O12" t="s">
+        <v>229</v>
+      </c>
+      <c r="P12" s="48">
+        <v>44858</v>
+      </c>
+      <c r="R12">
+        <v>0.26120649919613098</v>
+      </c>
+      <c r="S12" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" t="s">
         <v>232</v>
       </c>
-      <c r="CL11" s="7">
-        <v>104.2628</v>
-      </c>
-      <c r="CM11" s="7">
-        <v>0.45450000000000002</v>
-      </c>
-      <c r="CN11" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO11" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP11" s="7">
-        <v>24.1</v>
-      </c>
-      <c r="CQ11" s="7">
-        <v>-28.119</v>
-      </c>
-      <c r="CT11" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="CU11" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="CV11" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW11" s="15">
-        <v>99.284899999999993</v>
-      </c>
-      <c r="CX11" s="15">
-        <v>0.45579999999999998</v>
-      </c>
-      <c r="CY11" s="16">
-        <v>58</v>
-      </c>
-      <c r="CZ11" s="16">
+      <c r="U12" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="41">
+        <v>5.61</v>
+      </c>
+      <c r="W12" s="41">
+        <v>26.74</v>
+      </c>
+      <c r="X12" s="41">
+        <v>21.6</v>
+      </c>
+      <c r="Y12" s="41">
+        <v>24.39</v>
+      </c>
+      <c r="Z12" s="41">
+        <v>0.39</v>
+      </c>
+      <c r="AA12" s="41">
+        <v>23.73</v>
+      </c>
+      <c r="AB12" s="41">
+        <v>3.27</v>
+      </c>
+      <c r="AC12" s="41">
+        <v>1068.24</v>
+      </c>
+      <c r="AL12" s="41">
+        <v>1800</v>
+      </c>
+      <c r="AN12" s="41">
+        <v>-12.903705</v>
+      </c>
+      <c r="AP12" s="42"/>
+      <c r="AQ12" s="42"/>
+      <c r="AR12" s="42"/>
+      <c r="AS12" s="42"/>
+      <c r="BB12" s="47"/>
+      <c r="BC12" s="47"/>
+      <c r="BD12" s="47">
+        <f t="shared" si="2"/>
+        <v>5.61</v>
+      </c>
+      <c r="BF12" s="47">
+        <f t="shared" si="3"/>
+        <v>21.6</v>
+      </c>
+      <c r="BV12" s="47">
+        <f t="shared" si="4"/>
+        <v>-12.903705</v>
+      </c>
+      <c r="BZ12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="CA12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="CC12">
+        <v>297</v>
+      </c>
+      <c r="CD12">
+        <v>2022</v>
+      </c>
+      <c r="CG12" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH12" s="3">
+        <v>103.57470000000001</v>
+      </c>
+      <c r="CI12" s="3">
+        <v>0.47439999999999999</v>
+      </c>
+      <c r="CJ12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL12" s="3">
+        <v>17.489999999999998</v>
+      </c>
+      <c r="CM12" s="5">
+        <v>-27.276</v>
+      </c>
+      <c r="CR12" s="9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" s="13">
+        <v>43901</v>
+      </c>
+      <c r="C13">
+        <v>0.1</v>
+      </c>
+      <c r="D13">
+        <v>1.3</v>
+      </c>
+      <c r="E13">
+        <v>-1.3</v>
+      </c>
+      <c r="F13" t="s">
+        <v>227</v>
+      </c>
+      <c r="G13">
+        <v>0.8</v>
+      </c>
+      <c r="H13">
+        <v>2.1</v>
+      </c>
+      <c r="I13">
+        <v>2.1</v>
+      </c>
+      <c r="J13">
+        <v>6.7</v>
+      </c>
+      <c r="K13" t="s">
+        <v>227</v>
+      </c>
+      <c r="L13" t="s">
+        <v>227</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O13" t="s">
+        <v>228</v>
+      </c>
+      <c r="P13" s="49">
+        <v>43901</v>
+      </c>
+      <c r="R13">
+        <v>0.21519058331941299</v>
+      </c>
+      <c r="S13" t="s">
         <v>37</v>
       </c>
-      <c r="DA11" s="15">
-        <v>3.82</v>
-      </c>
-      <c r="DB11" s="17">
-        <v>-18.472999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P12" s="13">
-        <v>44858</v>
-      </c>
-      <c r="R12" s="2">
-        <v>0.56017182700000001</v>
-      </c>
-      <c r="S12">
+      <c r="T13" t="s">
+        <v>232</v>
+      </c>
+      <c r="U13" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="V13" s="45">
+        <v>5.3</v>
+      </c>
+      <c r="W13" s="45">
+        <v>30</v>
+      </c>
+      <c r="X13" s="45">
+        <v>10.8833</v>
+      </c>
+      <c r="Y13" s="45">
+        <v>4.76</v>
+      </c>
+      <c r="Z13" s="45">
+        <v>0.1991</v>
+      </c>
+      <c r="AA13" s="45">
+        <v>3.44</v>
+      </c>
+      <c r="AB13" s="45">
+        <v>2.19</v>
+      </c>
+      <c r="AC13" s="45">
+        <v>1630.79</v>
+      </c>
+      <c r="AL13" s="45">
+        <v>530.6164</v>
+      </c>
+      <c r="AN13" s="45">
+        <v>-13.01881</v>
+      </c>
+      <c r="AP13" s="46">
+        <v>2.4126384278196702</v>
+      </c>
+      <c r="AQ13" s="46">
+        <v>2542.34614259822</v>
+      </c>
+      <c r="AR13" s="46"/>
+      <c r="AS13" s="46">
+        <v>2.2882620626181902</v>
+      </c>
+      <c r="BB13" s="47">
         <f t="shared" si="0"/>
-        <v>48.398845852800001</v>
-      </c>
-      <c r="T12">
+        <v>2.2882620626181902</v>
+      </c>
+      <c r="BC13" s="47">
         <f t="shared" si="1"/>
-        <v>4.0332371544E-5</v>
-      </c>
-      <c r="U12" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12">
+        <v>2.4126384278196702</v>
+      </c>
+      <c r="BD13" s="47">
         <f t="shared" si="2"/>
-        <v>4.0332371544E-5</v>
-      </c>
-      <c r="W12" t="s">
-        <v>233</v>
-      </c>
-      <c r="X12" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y12" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z12" s="41">
-        <v>5.61</v>
-      </c>
-      <c r="AA12" s="41">
-        <v>26.74</v>
-      </c>
-      <c r="AB12" s="41">
-        <v>21.6</v>
-      </c>
-      <c r="AC12" s="41">
-        <v>24.39</v>
-      </c>
-      <c r="AD12" s="41">
-        <v>0.39</v>
-      </c>
-      <c r="AE12" s="41">
-        <v>23.73</v>
-      </c>
-      <c r="AF12" s="41">
-        <v>3.27</v>
-      </c>
-      <c r="AG12" s="41">
-        <v>1068.24</v>
-      </c>
-      <c r="AP12" s="41">
-        <v>1800</v>
-      </c>
-      <c r="AR12" s="41">
-        <v>-12.903705</v>
-      </c>
-      <c r="AT12" s="42"/>
-      <c r="AU12" s="42"/>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="BF12" s="47"/>
-      <c r="BG12" s="47"/>
-      <c r="BH12" s="47">
-        <f t="shared" si="5"/>
-        <v>5.61</v>
-      </c>
-      <c r="BJ12" s="47">
-        <f t="shared" si="6"/>
-        <v>21.6</v>
-      </c>
-      <c r="BZ12" s="47">
-        <f t="shared" si="7"/>
-        <v>-12.903705</v>
-      </c>
-      <c r="CD12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="CE12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="CF12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="CH12">
-        <v>2022</v>
-      </c>
-      <c r="CK12" t="s">
-        <v>232</v>
-      </c>
-      <c r="CL12" s="3">
-        <v>103.57470000000001</v>
-      </c>
-      <c r="CM12" s="3">
-        <v>0.47439999999999999</v>
-      </c>
-      <c r="CN12" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO12" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP12" s="3">
-        <v>17.489999999999998</v>
-      </c>
-      <c r="CQ12" s="5">
-        <v>-27.276</v>
-      </c>
-      <c r="CV12" s="9" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="13" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P13" s="26">
-        <v>43901</v>
-      </c>
-      <c r="R13">
-        <v>0.29887056499999998</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="0"/>
-        <v>25.822416816</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="1"/>
-        <v>2.1518680680000001E-5</v>
-      </c>
-      <c r="U13" t="s">
-        <v>37</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="2"/>
-        <v>2.1518680680000001E-5</v>
-      </c>
-      <c r="W13" t="s">
-        <v>233</v>
-      </c>
-      <c r="X13" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y13" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z13" s="45">
         <v>5.3</v>
-      </c>
-      <c r="AA13" s="45">
-        <v>30</v>
-      </c>
-      <c r="AB13" s="45">
-        <v>10.8833</v>
-      </c>
-      <c r="AC13" s="45">
-        <v>4.76</v>
-      </c>
-      <c r="AD13" s="45">
-        <v>0.1991</v>
-      </c>
-      <c r="AE13" s="45">
-        <v>3.44</v>
-      </c>
-      <c r="AF13" s="45">
-        <v>2.19</v>
-      </c>
-      <c r="AG13" s="45">
-        <v>1630.79</v>
-      </c>
-      <c r="AP13" s="45">
-        <v>530.6164</v>
-      </c>
-      <c r="AR13" s="45">
-        <v>-13.01881</v>
-      </c>
-      <c r="AT13" s="46">
-        <v>2.4126384278196702</v>
-      </c>
-      <c r="AU13" s="46">
-        <v>2542.34614259822</v>
-      </c>
-      <c r="AV13" s="46"/>
-      <c r="AW13" s="46">
-        <v>2.2882620626181902</v>
       </c>
       <c r="BF13" s="47">
         <f t="shared" si="3"/>
-        <v>2.2882620626181902</v>
-      </c>
-      <c r="BG13" s="47">
+        <v>10.8833</v>
+      </c>
+      <c r="BV13" s="47">
         <f t="shared" si="4"/>
-        <v>2.4126384278196702</v>
-      </c>
-      <c r="BH13" s="47">
-        <f t="shared" si="5"/>
-        <v>5.3</v>
-      </c>
-      <c r="BJ13" s="47">
-        <f t="shared" si="6"/>
-        <v>10.8833</v>
-      </c>
-      <c r="BZ13" s="47">
-        <f t="shared" si="7"/>
         <v>-13.01881</v>
       </c>
-      <c r="CD13" s="20" t="s">
+      <c r="BZ13" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="CE13" s="19" t="s">
+      <c r="CA13" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="CF13" s="19" t="s">
+      <c r="CB13" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="CH13">
+      <c r="CC13">
+        <v>71</v>
+      </c>
+      <c r="CD13">
         <v>2020</v>
       </c>
-      <c r="CK13" t="s">
+      <c r="CG13" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH13" s="21">
+        <v>100</v>
+      </c>
+      <c r="CI13" s="21">
+        <v>0.45739999999999997</v>
+      </c>
+      <c r="CJ13" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK13" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL13" s="21">
+        <v>7.63</v>
+      </c>
+      <c r="CM13" s="23">
+        <v>-28.693999999999999</v>
+      </c>
+      <c r="CP13" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="CQ13" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="CR13" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS13" s="28">
+        <v>103.1794</v>
+      </c>
+      <c r="CT13" s="29">
+        <v>0.47489999999999999</v>
+      </c>
+      <c r="CU13" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV13" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW13" s="29">
+        <v>5.24</v>
+      </c>
+      <c r="CX13" s="31">
+        <v>-22.867000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" s="13">
+        <v>43948</v>
+      </c>
+      <c r="C14">
+        <v>0.7</v>
+      </c>
+      <c r="D14">
+        <v>3.6</v>
+      </c>
+      <c r="E14">
+        <v>-2.8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>227</v>
+      </c>
+      <c r="G14">
+        <v>0.5</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>11.3</v>
+      </c>
+      <c r="J14">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K14">
+        <v>26</v>
+      </c>
+      <c r="L14" t="s">
+        <v>227</v>
+      </c>
+      <c r="M14">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="N14">
+        <v>6.5</v>
+      </c>
+      <c r="O14" t="s">
+        <v>228</v>
+      </c>
+      <c r="P14" s="49">
+        <v>43948</v>
+      </c>
+      <c r="R14">
+        <v>2.0148391226740499</v>
+      </c>
+      <c r="S14" t="s">
+        <v>37</v>
+      </c>
+      <c r="T14" t="s">
         <v>232</v>
       </c>
-      <c r="CL13" s="21">
-        <v>100</v>
-      </c>
-      <c r="CM13" s="21">
-        <v>0.45739999999999997</v>
-      </c>
-      <c r="CN13" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO13" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP13" s="21">
-        <v>7.63</v>
-      </c>
-      <c r="CQ13" s="23">
-        <v>-28.693999999999999</v>
-      </c>
-      <c r="CT13" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="CU13" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="CV13" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW13" s="28">
-        <v>103.1794</v>
-      </c>
-      <c r="CX13" s="29">
-        <v>0.47489999999999999</v>
-      </c>
-      <c r="CY13" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="CZ13" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="DA13" s="29">
-        <v>5.24</v>
-      </c>
-      <c r="DB13" s="31">
-        <v>-22.867000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P14" s="13">
-        <v>43948</v>
-      </c>
-      <c r="R14" s="2">
-        <v>2.7977782000000002</v>
-      </c>
-      <c r="S14">
+      <c r="U14" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="V14" s="45">
+        <v>4.72</v>
+      </c>
+      <c r="W14" s="45">
+        <v>30</v>
+      </c>
+      <c r="X14" s="45">
+        <v>23.146699999999999</v>
+      </c>
+      <c r="Y14" s="45">
+        <v>7.32</v>
+      </c>
+      <c r="Z14" s="45">
+        <v>0.37609999999999999</v>
+      </c>
+      <c r="AA14" s="45">
+        <v>5.68</v>
+      </c>
+      <c r="AB14" s="45">
+        <v>1.72</v>
+      </c>
+      <c r="AC14" s="45">
+        <v>1147.3699999999999</v>
+      </c>
+      <c r="AL14" s="45">
+        <v>864.38670000000002</v>
+      </c>
+      <c r="AN14" s="45">
+        <v>-13.47376</v>
+      </c>
+      <c r="AP14" s="46">
+        <v>1.53228854349357</v>
+      </c>
+      <c r="AQ14" s="46">
+        <v>1695.3964687151099</v>
+      </c>
+      <c r="AR14" s="46"/>
+      <c r="AS14" s="46">
+        <v>1.5104388139343099</v>
+      </c>
+      <c r="BB14" s="47">
         <f t="shared" si="0"/>
-        <v>241.72803648000001</v>
-      </c>
-      <c r="T14">
+        <v>1.5104388139343099</v>
+      </c>
+      <c r="BC14" s="47">
         <f t="shared" si="1"/>
-        <v>2.014400304E-4</v>
-      </c>
-      <c r="U14" t="s">
-        <v>37</v>
-      </c>
-      <c r="V14">
+        <v>1.53228854349357</v>
+      </c>
+      <c r="BD14" s="47">
         <f t="shared" si="2"/>
-        <v>2.014400304E-4</v>
-      </c>
-      <c r="W14" t="s">
-        <v>233</v>
-      </c>
-      <c r="X14" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y14" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z14" s="45">
         <v>4.72</v>
-      </c>
-      <c r="AA14" s="45">
-        <v>30</v>
-      </c>
-      <c r="AB14" s="45">
-        <v>23.146699999999999</v>
-      </c>
-      <c r="AC14" s="45">
-        <v>7.32</v>
-      </c>
-      <c r="AD14" s="45">
-        <v>0.37609999999999999</v>
-      </c>
-      <c r="AE14" s="45">
-        <v>5.68</v>
-      </c>
-      <c r="AF14" s="45">
-        <v>1.72</v>
-      </c>
-      <c r="AG14" s="45">
-        <v>1147.3699999999999</v>
-      </c>
-      <c r="AP14" s="45">
-        <v>864.38670000000002</v>
-      </c>
-      <c r="AR14" s="45">
-        <v>-13.47376</v>
-      </c>
-      <c r="AT14" s="46">
-        <v>1.53228854349357</v>
-      </c>
-      <c r="AU14" s="46">
-        <v>1695.3964687151099</v>
-      </c>
-      <c r="AV14" s="46"/>
-      <c r="AW14" s="46">
-        <v>1.5104388139343099</v>
       </c>
       <c r="BF14" s="47">
         <f t="shared" si="3"/>
-        <v>1.5104388139343099</v>
-      </c>
-      <c r="BG14" s="47">
+        <v>23.146699999999999</v>
+      </c>
+      <c r="BV14" s="47">
         <f t="shared" si="4"/>
-        <v>1.53228854349357</v>
-      </c>
-      <c r="BH14" s="47">
-        <f t="shared" si="5"/>
-        <v>4.72</v>
-      </c>
-      <c r="BJ14" s="47">
-        <f t="shared" si="6"/>
-        <v>23.146699999999999</v>
-      </c>
-      <c r="BZ14" s="47">
-        <f t="shared" si="7"/>
         <v>-13.47376</v>
       </c>
-      <c r="CD14" s="2" t="s">
+      <c r="BZ14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="CE14" s="1" t="s">
+      <c r="CA14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="CF14" s="1" t="s">
+      <c r="CB14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="CH14">
+      <c r="CC14">
+        <v>118</v>
+      </c>
+      <c r="CD14">
         <v>2020</v>
       </c>
-      <c r="CK14" t="s">
+      <c r="CG14" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH14" s="3">
+        <v>105.7137</v>
+      </c>
+      <c r="CI14" s="3">
+        <v>0.48570000000000002</v>
+      </c>
+      <c r="CJ14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL14" s="5">
+        <v>18.3</v>
+      </c>
+      <c r="CM14" s="5">
+        <v>-28.968</v>
+      </c>
+      <c r="CR14" s="9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15" s="13">
+        <v>44071</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>16.7</v>
+      </c>
+      <c r="E15">
+        <v>3.4</v>
+      </c>
+      <c r="F15" t="s">
+        <v>227</v>
+      </c>
+      <c r="G15">
+        <v>10.6</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>12.1</v>
+      </c>
+      <c r="J15">
+        <v>9.6</v>
+      </c>
+      <c r="K15">
+        <v>27</v>
+      </c>
+      <c r="L15">
+        <v>6</v>
+      </c>
+      <c r="M15">
+        <v>1.2</v>
+      </c>
+      <c r="N15">
+        <v>3.8</v>
+      </c>
+      <c r="O15" t="s">
+        <v>228</v>
+      </c>
+      <c r="P15" s="49">
+        <v>44071</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15" t="s">
+        <v>37</v>
+      </c>
+      <c r="T15" t="s">
         <v>232</v>
-      </c>
-      <c r="CL14" s="3">
-        <v>105.7137</v>
-      </c>
-      <c r="CM14" s="3">
-        <v>0.48570000000000002</v>
-      </c>
-      <c r="CN14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP14" s="5">
-        <v>18.3</v>
-      </c>
-      <c r="CQ14" s="5">
-        <v>-28.968</v>
-      </c>
-      <c r="CV14" s="9" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P15" s="13">
-        <v>44071</v>
-      </c>
-      <c r="R15">
-        <v>1.7957520000000001E-3</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="0"/>
-        <v>0.15515297280000001</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="1"/>
-        <v>1.2929414400000001E-7</v>
       </c>
       <c r="U15" t="s">
         <v>37</v>
       </c>
       <c r="V15">
+        <v>5.26</v>
+      </c>
+      <c r="W15">
+        <v>35</v>
+      </c>
+      <c r="X15">
+        <v>15.90335</v>
+      </c>
+      <c r="Y15">
+        <v>7.43</v>
+      </c>
+      <c r="Z15">
+        <v>0.30004999999999998</v>
+      </c>
+      <c r="AA15">
+        <v>11.120000000000001</v>
+      </c>
+      <c r="AB15">
+        <v>11.21</v>
+      </c>
+      <c r="AC15">
+        <v>1910.0650000000001</v>
+      </c>
+      <c r="AL15">
+        <v>673.25350000000003</v>
+      </c>
+      <c r="AN15">
+        <v>-13.2013905</v>
+      </c>
+      <c r="AP15">
+        <v>9.2250958521134052</v>
+      </c>
+      <c r="AR15">
+        <v>15.864106259692075</v>
+      </c>
+      <c r="AS15">
+        <f>AP15</f>
+        <v>9.2250958521134052</v>
+      </c>
+      <c r="BB15" s="47">
+        <f t="shared" si="0"/>
+        <v>9.2250958521134052</v>
+      </c>
+      <c r="BC15" s="47">
+        <f t="shared" si="1"/>
+        <v>9.2250958521134052</v>
+      </c>
+      <c r="BD15" s="47">
         <f t="shared" si="2"/>
-        <v>1.2929414400000001E-7</v>
-      </c>
-      <c r="W15" t="s">
-        <v>233</v>
-      </c>
-      <c r="X15" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z15">
         <v>5.26</v>
-      </c>
-      <c r="AA15">
-        <v>35</v>
-      </c>
-      <c r="AB15">
-        <v>15.90335</v>
-      </c>
-      <c r="AC15">
-        <v>7.43</v>
-      </c>
-      <c r="AD15">
-        <v>0.30004999999999998</v>
-      </c>
-      <c r="AE15">
-        <v>11.120000000000001</v>
-      </c>
-      <c r="AF15">
-        <v>11.21</v>
-      </c>
-      <c r="AG15">
-        <v>1910.0650000000001</v>
-      </c>
-      <c r="AP15">
-        <v>673.25350000000003</v>
-      </c>
-      <c r="AR15">
-        <v>-13.2013905</v>
-      </c>
-      <c r="AT15">
-        <v>9.2250958521134052</v>
-      </c>
-      <c r="AV15">
-        <v>15.864106259692075</v>
-      </c>
-      <c r="AW15">
-        <f>AT15</f>
-        <v>9.2250958521134052</v>
       </c>
       <c r="BF15" s="47">
         <f t="shared" si="3"/>
-        <v>9.2250958521134052</v>
-      </c>
-      <c r="BG15" s="47">
+        <v>15.90335</v>
+      </c>
+      <c r="BV15" s="47">
         <f t="shared" si="4"/>
-        <v>9.2250958521134052</v>
-      </c>
-      <c r="BH15" s="47">
-        <f t="shared" si="5"/>
-        <v>5.26</v>
-      </c>
-      <c r="BJ15" s="47">
-        <f t="shared" si="6"/>
-        <v>15.90335</v>
-      </c>
-      <c r="BZ15" s="47">
-        <f t="shared" si="7"/>
         <v>-13.2013905</v>
       </c>
-      <c r="CD15" s="2" t="s">
+      <c r="BZ15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="CE15" s="1" t="s">
+      <c r="CA15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="CF15" s="1" t="s">
+      <c r="CB15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="CH15">
+      <c r="CC15">
+        <v>241</v>
+      </c>
+      <c r="CD15">
         <v>2020</v>
       </c>
-      <c r="CK15" t="s">
+      <c r="CG15" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH15" s="3">
+        <v>104.4345</v>
+      </c>
+      <c r="CI15" s="3">
+        <v>0.47960000000000003</v>
+      </c>
+      <c r="CJ15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL15" s="5">
+        <v>43</v>
+      </c>
+      <c r="CM15" s="5">
+        <v>-28.7</v>
+      </c>
+      <c r="CP15" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="CQ15" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="CR15" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS15" s="14">
+        <v>104.1057</v>
+      </c>
+      <c r="CT15" s="15">
+        <v>0.4536</v>
+      </c>
+      <c r="CU15" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV15" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW15" s="15">
+        <v>7.28</v>
+      </c>
+      <c r="CX15" s="17">
+        <v>-24.890999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" s="13">
+        <v>44125</v>
+      </c>
+      <c r="C16">
+        <v>-0.2</v>
+      </c>
+      <c r="D16">
+        <v>0.7</v>
+      </c>
+      <c r="E16">
+        <v>-1.8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>227</v>
+      </c>
+      <c r="G16">
+        <v>4.7</v>
+      </c>
+      <c r="H16">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I16">
+        <v>0.9</v>
+      </c>
+      <c r="J16">
+        <v>6.5</v>
+      </c>
+      <c r="K16" t="s">
+        <v>227</v>
+      </c>
+      <c r="L16">
+        <v>-0.9</v>
+      </c>
+      <c r="M16">
+        <v>3.9</v>
+      </c>
+      <c r="N16">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="O16" t="s">
+        <v>228</v>
+      </c>
+      <c r="P16" s="49">
+        <v>44125</v>
+      </c>
+      <c r="R16">
+        <v>0.705102278582596</v>
+      </c>
+      <c r="S16" t="s">
+        <v>37</v>
+      </c>
+      <c r="T16" t="s">
         <v>232</v>
       </c>
-      <c r="CL15" s="3">
-        <v>104.4345</v>
-      </c>
-      <c r="CM15" s="3">
-        <v>0.47960000000000003</v>
-      </c>
-      <c r="CN15" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO15" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP15" s="5">
-        <v>43</v>
-      </c>
-      <c r="CQ15" s="5">
-        <v>-28.7</v>
-      </c>
-      <c r="CT15" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="CU15" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="CV15" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW15" s="14">
-        <v>104.1057</v>
-      </c>
-      <c r="CX15" s="15">
-        <v>0.4536</v>
-      </c>
-      <c r="CY15" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="CZ15" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="DA15" s="15">
-        <v>7.28</v>
-      </c>
-      <c r="DB15" s="17">
-        <v>-24.890999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="2:106" x14ac:dyDescent="0.2">
-      <c r="P16" s="13">
-        <v>44125</v>
-      </c>
-      <c r="R16" s="2">
-        <v>0.98031077300000002</v>
-      </c>
-      <c r="S16">
+      <c r="U16" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="V16" s="45">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="W16" s="45">
+        <v>33</v>
+      </c>
+      <c r="X16" s="45">
+        <v>23.5</v>
+      </c>
+      <c r="Y16" s="45">
+        <v>6.7</v>
+      </c>
+      <c r="Z16" s="45">
+        <v>0.38</v>
+      </c>
+      <c r="AA16" s="45">
+        <v>5.27</v>
+      </c>
+      <c r="AB16" s="45">
+        <v>5.84</v>
+      </c>
+      <c r="AC16" s="45">
+        <v>1489.79</v>
+      </c>
+      <c r="AL16" s="45">
+        <v>1021.1128</v>
+      </c>
+      <c r="AN16" s="45">
+        <v>-13.019297</v>
+      </c>
+      <c r="AP16" s="46">
+        <v>2.3439550277055399</v>
+      </c>
+      <c r="AQ16" s="46">
+        <v>2808.3906590654401</v>
+      </c>
+      <c r="AR16" s="46"/>
+      <c r="AS16" s="46">
+        <v>2.3109001218860699</v>
+      </c>
+      <c r="BB16" s="47">
         <f t="shared" si="0"/>
-        <v>84.698850787200001</v>
-      </c>
-      <c r="T16">
+        <v>2.3109001218860699</v>
+      </c>
+      <c r="BC16" s="47">
         <f t="shared" si="1"/>
-        <v>7.0582375655999996E-5</v>
-      </c>
-      <c r="U16" t="s">
-        <v>37</v>
-      </c>
-      <c r="V16">
+        <v>2.3439550277055399</v>
+      </c>
+      <c r="BD16" s="47">
         <f t="shared" si="2"/>
-        <v>7.0582375655999996E-5</v>
-      </c>
-      <c r="W16" t="s">
-        <v>233</v>
-      </c>
-      <c r="X16" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y16" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z16" s="45">
         <v>4.6900000000000004</v>
-      </c>
-      <c r="AA16" s="45">
-        <v>33</v>
-      </c>
-      <c r="AB16" s="45">
-        <v>23.5</v>
-      </c>
-      <c r="AC16" s="45">
-        <v>6.7</v>
-      </c>
-      <c r="AD16" s="45">
-        <v>0.38</v>
-      </c>
-      <c r="AE16" s="45">
-        <v>5.27</v>
-      </c>
-      <c r="AF16" s="45">
-        <v>5.84</v>
-      </c>
-      <c r="AG16" s="45">
-        <v>1489.79</v>
-      </c>
-      <c r="AP16" s="45">
-        <v>1021.1128</v>
-      </c>
-      <c r="AR16" s="45">
-        <v>-13.019297</v>
-      </c>
-      <c r="AT16" s="46">
-        <v>2.3439550277055399</v>
-      </c>
-      <c r="AU16" s="46">
-        <v>2808.3906590654401</v>
-      </c>
-      <c r="AV16" s="46"/>
-      <c r="AW16" s="46">
-        <v>2.3109001218860699</v>
       </c>
       <c r="BF16" s="47">
         <f t="shared" si="3"/>
-        <v>2.3109001218860699</v>
-      </c>
-      <c r="BG16" s="47">
+        <v>23.5</v>
+      </c>
+      <c r="BV16" s="47">
         <f t="shared" si="4"/>
-        <v>2.3439550277055399</v>
-      </c>
-      <c r="BH16" s="47">
-        <f t="shared" si="5"/>
-        <v>4.6900000000000004</v>
-      </c>
-      <c r="BJ16" s="47">
-        <f t="shared" si="6"/>
-        <v>23.5</v>
-      </c>
-      <c r="BZ16" s="47">
-        <f t="shared" si="7"/>
         <v>-13.019297</v>
       </c>
-      <c r="CD16" s="2" t="s">
+      <c r="BZ16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="CE16" s="1" t="s">
+      <c r="CA16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="CF16" s="1" t="s">
+      <c r="CB16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="CH16">
+      <c r="CC16">
+        <v>295</v>
+      </c>
+      <c r="CD16">
         <v>2020</v>
       </c>
-      <c r="CK16" t="s">
+      <c r="CG16" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH16" s="3">
+        <v>108.0196</v>
+      </c>
+      <c r="CI16" s="3">
+        <v>0.48430000000000001</v>
+      </c>
+      <c r="CJ16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL16" s="3">
+        <v>23.91</v>
+      </c>
+      <c r="CM16" s="5">
+        <v>-29.324999999999999</v>
+      </c>
+      <c r="CP16" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="CQ16" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="CR16" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS16" s="14">
+        <v>103.3997</v>
+      </c>
+      <c r="CT16" s="15">
+        <v>0.49020000000000002</v>
+      </c>
+      <c r="CU16" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV16" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW16" s="15">
+        <v>4.28</v>
+      </c>
+      <c r="CX16" s="17">
+        <v>-22.738</v>
+      </c>
+    </row>
+    <row r="17" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17" s="13">
+        <v>44315</v>
+      </c>
+      <c r="C17">
+        <v>0.8</v>
+      </c>
+      <c r="D17">
+        <v>5.5</v>
+      </c>
+      <c r="E17">
+        <v>-5.3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>227</v>
+      </c>
+      <c r="G17">
+        <v>0.8</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>17.3</v>
+      </c>
+      <c r="J17">
+        <v>3.8</v>
+      </c>
+      <c r="K17">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>2.4</v>
+      </c>
+      <c r="N17">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="O17" t="s">
+        <v>228</v>
+      </c>
+      <c r="P17" s="49">
+        <v>44315</v>
+      </c>
+      <c r="R17">
+        <v>1.42652935508005</v>
+      </c>
+      <c r="S17" t="s">
+        <v>37</v>
+      </c>
+      <c r="T17" t="s">
         <v>232</v>
       </c>
-      <c r="CL16" s="3">
-        <v>108.0196</v>
-      </c>
-      <c r="CM16" s="3">
-        <v>0.48430000000000001</v>
-      </c>
-      <c r="CN16" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO16" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP16" s="3">
-        <v>23.91</v>
-      </c>
-      <c r="CQ16" s="5">
-        <v>-29.324999999999999</v>
-      </c>
-      <c r="CT16" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="CU16" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="CV16" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW16" s="14">
-        <v>103.3997</v>
-      </c>
-      <c r="CX16" s="15">
-        <v>0.49020000000000002</v>
-      </c>
-      <c r="CY16" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="CZ16" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="DA16" s="15">
-        <v>4.28</v>
-      </c>
-      <c r="DB16" s="17">
-        <v>-22.738</v>
-      </c>
-    </row>
-    <row r="17" spans="16:106" x14ac:dyDescent="0.2">
-      <c r="P17" s="13">
-        <v>44315</v>
-      </c>
-      <c r="R17" s="2">
-        <v>1.9812636960000001</v>
-      </c>
-      <c r="S17">
+      <c r="U17" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="V17" s="41">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="W17" s="41">
+        <v>23.46</v>
+      </c>
+      <c r="X17" s="41">
+        <v>18.2</v>
+      </c>
+      <c r="Y17" s="41">
+        <v>6.54</v>
+      </c>
+      <c r="Z17" s="41">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AA17" s="41">
+        <v>4.21</v>
+      </c>
+      <c r="AB17" s="41">
+        <v>2.95</v>
+      </c>
+      <c r="AC17" s="41">
+        <v>1111.73</v>
+      </c>
+      <c r="AL17" s="41">
+        <v>641.4384</v>
+      </c>
+      <c r="AN17" s="41">
+        <v>-13.654695</v>
+      </c>
+      <c r="AP17" s="42">
+        <v>1.2142766025215199</v>
+      </c>
+      <c r="AQ17" s="42"/>
+      <c r="AR17" s="42"/>
+      <c r="AS17" s="42">
+        <f>AP17</f>
+        <v>1.2142766025215199</v>
+      </c>
+      <c r="BB17" s="47">
         <f t="shared" si="0"/>
-        <v>171.1811833344</v>
-      </c>
-      <c r="T17">
+        <v>1.2142766025215199</v>
+      </c>
+      <c r="BC17" s="47">
         <f t="shared" si="1"/>
-        <v>1.42650986112E-4</v>
-      </c>
-      <c r="U17" t="s">
-        <v>37</v>
-      </c>
-      <c r="V17">
+        <v>1.2142766025215199</v>
+      </c>
+      <c r="BD17" s="47">
         <f t="shared" si="2"/>
-        <v>1.42650986112E-4</v>
-      </c>
-      <c r="W17" t="s">
-        <v>233</v>
-      </c>
-      <c r="X17" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y17" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z17" s="41">
         <v>4.7300000000000004</v>
-      </c>
-      <c r="AA17" s="41">
-        <v>23.46</v>
-      </c>
-      <c r="AB17" s="41">
-        <v>18.2</v>
-      </c>
-      <c r="AC17" s="41">
-        <v>6.54</v>
-      </c>
-      <c r="AD17" s="41">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AE17" s="41">
-        <v>4.21</v>
-      </c>
-      <c r="AF17" s="41">
-        <v>2.95</v>
-      </c>
-      <c r="AG17" s="41">
-        <v>1111.73</v>
-      </c>
-      <c r="AP17" s="41">
-        <v>641.4384</v>
-      </c>
-      <c r="AR17" s="41">
-        <v>-13.654695</v>
-      </c>
-      <c r="AT17" s="42">
-        <v>1.2142766025215199</v>
-      </c>
-      <c r="AU17" s="42"/>
-      <c r="AV17" s="42"/>
-      <c r="AW17" s="42">
-        <f>AT17</f>
-        <v>1.2142766025215199</v>
       </c>
       <c r="BF17" s="47">
         <f t="shared" si="3"/>
-        <v>1.2142766025215199</v>
-      </c>
-      <c r="BG17" s="47">
+        <v>18.2</v>
+      </c>
+      <c r="BV17" s="47">
         <f t="shared" si="4"/>
-        <v>1.2142766025215199</v>
-      </c>
-      <c r="BH17" s="47">
-        <f t="shared" si="5"/>
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="BJ17" s="47">
-        <f t="shared" si="6"/>
-        <v>18.2</v>
-      </c>
-      <c r="BZ17" s="47">
-        <f t="shared" si="7"/>
         <v>-13.654695</v>
       </c>
-      <c r="CD17" s="2" t="s">
+      <c r="BZ17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="CE17" s="1" t="s">
+      <c r="CA17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="CF17" s="1" t="s">
+      <c r="CB17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="CH17">
+      <c r="CC17">
+        <v>119</v>
+      </c>
+      <c r="CD17">
         <v>2021</v>
       </c>
-      <c r="CK17" t="s">
+      <c r="CG17" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH17" s="3">
+        <v>106.7024</v>
+      </c>
+      <c r="CI17" s="3">
+        <v>0.48770000000000002</v>
+      </c>
+      <c r="CJ17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL17" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="CM17" s="5">
+        <v>-28.53</v>
+      </c>
+      <c r="CP17" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="CQ17" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="CR17" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS17" s="14">
+        <v>102.29170000000001</v>
+      </c>
+      <c r="CT17" s="15">
+        <v>0.48380000000000001</v>
+      </c>
+      <c r="CU17" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV17" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW17" s="15">
+        <v>2.73</v>
+      </c>
+      <c r="CX17" s="17">
+        <v>-19.221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18" s="13">
+        <v>44427</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18">
+        <v>16.2</v>
+      </c>
+      <c r="E18">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F18" t="s">
+        <v>227</v>
+      </c>
+      <c r="G18">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>3.4</v>
+      </c>
+      <c r="I18">
+        <v>9.5</v>
+      </c>
+      <c r="J18">
+        <v>13.2</v>
+      </c>
+      <c r="K18">
+        <v>23.2</v>
+      </c>
+      <c r="L18">
+        <v>3.5</v>
+      </c>
+      <c r="M18">
+        <v>1.3</v>
+      </c>
+      <c r="N18">
+        <v>5.6</v>
+      </c>
+      <c r="O18" t="s">
+        <v>228</v>
+      </c>
+      <c r="P18" s="49">
+        <v>44427</v>
+      </c>
+      <c r="R18">
+        <v>1.50187150171214</v>
+      </c>
+      <c r="S18" t="s">
+        <v>37</v>
+      </c>
+      <c r="T18" t="s">
         <v>232</v>
       </c>
-      <c r="CL17" s="3">
-        <v>106.7024</v>
-      </c>
-      <c r="CM17" s="3">
-        <v>0.48770000000000002</v>
-      </c>
-      <c r="CN17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP17" s="3">
-        <v>14.5</v>
-      </c>
-      <c r="CQ17" s="5">
-        <v>-28.53</v>
-      </c>
-      <c r="CT17" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="CU17" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="CV17" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW17" s="14">
-        <v>102.29170000000001</v>
-      </c>
-      <c r="CX17" s="15">
-        <v>0.48380000000000001</v>
-      </c>
-      <c r="CY17" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="CZ17" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="DA17" s="15">
-        <v>2.73</v>
-      </c>
-      <c r="DB17" s="17">
-        <v>-19.221</v>
-      </c>
-    </row>
-    <row r="18" spans="16:106" x14ac:dyDescent="0.2">
-      <c r="P18" s="13">
-        <v>44427</v>
-      </c>
-      <c r="R18" s="2">
-        <v>2.0836396480000001</v>
-      </c>
-      <c r="S18">
+      <c r="U18" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="V18" s="41">
+        <v>4.83</v>
+      </c>
+      <c r="W18" s="41">
+        <v>28.61</v>
+      </c>
+      <c r="X18" s="41">
+        <v>30.15</v>
+      </c>
+      <c r="Y18" s="41">
+        <v>9.61</v>
+      </c>
+      <c r="Z18" s="41">
+        <v>0.49</v>
+      </c>
+      <c r="AA18" s="41">
+        <v>8.5549999999999997</v>
+      </c>
+      <c r="AB18" s="41">
+        <v>5.2850000000000001</v>
+      </c>
+      <c r="AC18" s="41">
+        <v>931.59550000000002</v>
+      </c>
+      <c r="AL18" s="41">
+        <v>1613.0462</v>
+      </c>
+      <c r="AN18" s="41">
+        <v>-12.885248000000001</v>
+      </c>
+      <c r="AP18" s="41">
+        <v>2.6900092390010251</v>
+      </c>
+      <c r="AQ18" s="41"/>
+      <c r="AR18" s="41">
+        <v>2.9837654456601199</v>
+      </c>
+      <c r="AS18" s="41">
+        <f>AP18</f>
+        <v>2.6900092390010251</v>
+      </c>
+      <c r="BB18" s="47">
         <f t="shared" si="0"/>
-        <v>180.02646558719999</v>
-      </c>
-      <c r="T18">
+        <v>2.6900092390010251</v>
+      </c>
+      <c r="BC18" s="47">
         <f t="shared" si="1"/>
-        <v>1.50022054656E-4</v>
-      </c>
-      <c r="U18" t="s">
-        <v>37</v>
-      </c>
-      <c r="V18">
+        <v>2.6900092390010251</v>
+      </c>
+      <c r="BD18" s="47">
         <f t="shared" si="2"/>
-        <v>1.50022054656E-4</v>
-      </c>
-      <c r="W18" t="s">
-        <v>233</v>
-      </c>
-      <c r="X18" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y18" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z18" s="41">
         <v>4.83</v>
-      </c>
-      <c r="AA18" s="41">
-        <v>28.61</v>
-      </c>
-      <c r="AB18" s="41">
-        <v>30.15</v>
-      </c>
-      <c r="AC18" s="41">
-        <v>9.61</v>
-      </c>
-      <c r="AD18" s="41">
-        <v>0.49</v>
-      </c>
-      <c r="AE18" s="41">
-        <v>8.5549999999999997</v>
-      </c>
-      <c r="AF18" s="41">
-        <v>5.2850000000000001</v>
-      </c>
-      <c r="AG18" s="41">
-        <v>931.59550000000002</v>
-      </c>
-      <c r="AP18" s="41">
-        <v>1613.0462</v>
-      </c>
-      <c r="AR18" s="41">
-        <v>-12.885248000000001</v>
-      </c>
-      <c r="AT18" s="41">
-        <v>2.6900092390010251</v>
-      </c>
-      <c r="AU18" s="41"/>
-      <c r="AV18" s="41">
-        <v>2.9837654456601199</v>
-      </c>
-      <c r="AW18" s="41">
-        <f>AT18</f>
-        <v>2.6900092390010251</v>
       </c>
       <c r="BF18" s="47">
         <f t="shared" si="3"/>
-        <v>2.6900092390010251</v>
-      </c>
-      <c r="BG18" s="47">
+        <v>30.15</v>
+      </c>
+      <c r="BV18" s="47">
         <f t="shared" si="4"/>
-        <v>2.6900092390010251</v>
-      </c>
-      <c r="BH18" s="47">
-        <f t="shared" si="5"/>
-        <v>4.83</v>
-      </c>
-      <c r="BJ18" s="47">
-        <f t="shared" si="6"/>
-        <v>30.15</v>
-      </c>
-      <c r="BZ18" s="47">
-        <f t="shared" si="7"/>
         <v>-12.885248000000001</v>
       </c>
-      <c r="CD18" s="2" t="s">
+      <c r="BZ18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="CE18" s="1" t="s">
+      <c r="CA18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="CF18" s="1" t="s">
+      <c r="CB18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="CH18">
+      <c r="CC18">
+        <v>231</v>
+      </c>
+      <c r="CD18">
         <v>2021</v>
       </c>
-      <c r="CK18" t="s">
+      <c r="CG18" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH18" s="3">
+        <v>106.13639999999999</v>
+      </c>
+      <c r="CI18" s="3">
+        <v>0.46239999999999998</v>
+      </c>
+      <c r="CJ18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL18" s="3">
+        <v>39.36</v>
+      </c>
+      <c r="CM18" s="5">
+        <v>-29.097999999999999</v>
+      </c>
+      <c r="CP18" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="CQ18" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="CR18" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS18" s="14">
+        <v>104.8813</v>
+      </c>
+      <c r="CT18" s="15">
+        <v>0.48110000000000003</v>
+      </c>
+      <c r="CU18" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV18" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW18" s="15">
+        <v>3.26</v>
+      </c>
+      <c r="CX18" s="17">
+        <v>-22.181999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>7</v>
+      </c>
+      <c r="B19" s="13">
+        <v>44464</v>
+      </c>
+      <c r="C19">
+        <v>5.4</v>
+      </c>
+      <c r="D19">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>227</v>
+      </c>
+      <c r="G19">
+        <v>7.8</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>3.6</v>
+      </c>
+      <c r="J19">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="K19">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="L19">
+        <v>-0.4</v>
+      </c>
+      <c r="M19">
+        <v>2.5</v>
+      </c>
+      <c r="N19">
+        <v>10.7</v>
+      </c>
+      <c r="O19" t="s">
+        <v>228</v>
+      </c>
+      <c r="P19" s="49">
+        <v>44464</v>
+      </c>
+      <c r="R19">
+        <v>3.4877404926156998</v>
+      </c>
+      <c r="S19" t="s">
+        <v>37</v>
+      </c>
+      <c r="T19" t="s">
         <v>232</v>
       </c>
-      <c r="CL18" s="3">
-        <v>106.13639999999999</v>
-      </c>
-      <c r="CM18" s="3">
-        <v>0.46239999999999998</v>
-      </c>
-      <c r="CN18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP18" s="3">
-        <v>39.36</v>
-      </c>
-      <c r="CQ18" s="5">
-        <v>-29.097999999999999</v>
-      </c>
-      <c r="CT18" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="CU18" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="CV18" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW18" s="14">
-        <v>104.8813</v>
-      </c>
-      <c r="CX18" s="15">
-        <v>0.48110000000000003</v>
-      </c>
-      <c r="CY18" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="CZ18" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="DA18" s="15">
-        <v>3.26</v>
-      </c>
-      <c r="DB18" s="17">
-        <v>-22.181999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="16:106" x14ac:dyDescent="0.2">
-      <c r="P19" s="13">
-        <v>44493</v>
-      </c>
-      <c r="R19" s="2">
-        <v>4.8347428949999998</v>
-      </c>
-      <c r="S19">
+      <c r="U19" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="V19" s="45">
+        <v>4.5</v>
+      </c>
+      <c r="W19" s="45">
+        <v>32.99</v>
+      </c>
+      <c r="X19" s="45">
+        <v>35.6</v>
+      </c>
+      <c r="Y19" s="45">
+        <v>9.39</v>
+      </c>
+      <c r="Z19" s="45">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AA19" s="45">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="AB19" s="45">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="AC19" s="45">
+        <v>953.71500000000003</v>
+      </c>
+      <c r="AL19" s="45">
+        <v>1588.9444000000001</v>
+      </c>
+      <c r="AN19" s="45">
+        <v>-12.691136999999999</v>
+      </c>
+      <c r="AP19" s="46">
+        <v>1.8093386698979299</v>
+      </c>
+      <c r="AQ19" s="46"/>
+      <c r="AR19" s="46"/>
+      <c r="AS19" s="46">
+        <f>AP19</f>
+        <v>1.8093386698979299</v>
+      </c>
+      <c r="BB19" s="47">
         <f t="shared" si="0"/>
-        <v>417.72178612800008</v>
-      </c>
-      <c r="T19">
+        <v>1.8093386698979299</v>
+      </c>
+      <c r="BC19" s="47">
         <f t="shared" si="1"/>
-        <v>3.4810148844000005E-4</v>
-      </c>
-      <c r="U19" t="s">
-        <v>37</v>
-      </c>
-      <c r="V19">
+        <v>1.8093386698979299</v>
+      </c>
+      <c r="BD19" s="47">
         <f t="shared" si="2"/>
-        <v>3.4810148844000005E-4</v>
-      </c>
-      <c r="W19" t="s">
-        <v>233</v>
-      </c>
-      <c r="X19" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y19" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z19" s="45">
         <v>4.5</v>
-      </c>
-      <c r="AA19" s="45">
-        <v>32.99</v>
-      </c>
-      <c r="AB19" s="45">
-        <v>35.6</v>
-      </c>
-      <c r="AC19" s="45">
-        <v>9.39</v>
-      </c>
-      <c r="AD19" s="45">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="AE19" s="45">
-        <v>9.7899999999999991</v>
-      </c>
-      <c r="AF19" s="45">
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="AG19" s="45">
-        <v>953.71500000000003</v>
-      </c>
-      <c r="AP19" s="45">
-        <v>1588.9444000000001</v>
-      </c>
-      <c r="AR19" s="45">
-        <v>-12.691136999999999</v>
-      </c>
-      <c r="AT19" s="46">
-        <v>1.8093386698979299</v>
-      </c>
-      <c r="AU19" s="46"/>
-      <c r="AV19" s="46"/>
-      <c r="AW19" s="46">
-        <f>AT19</f>
-        <v>1.8093386698979299</v>
       </c>
       <c r="BF19" s="47">
         <f t="shared" si="3"/>
-        <v>1.8093386698979299</v>
-      </c>
-      <c r="BG19" s="47">
+        <v>35.6</v>
+      </c>
+      <c r="BV19" s="47">
         <f t="shared" si="4"/>
-        <v>1.8093386698979299</v>
-      </c>
-      <c r="BH19" s="47">
-        <f t="shared" si="5"/>
-        <v>4.5</v>
-      </c>
-      <c r="BJ19" s="47">
-        <f t="shared" si="6"/>
-        <v>35.6</v>
-      </c>
-      <c r="BZ19" s="47">
-        <f t="shared" si="7"/>
         <v>-12.691136999999999</v>
       </c>
-      <c r="CD19" s="2" t="s">
+      <c r="BZ19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="CE19" s="1" t="s">
+      <c r="CA19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="CF19" s="1" t="s">
+      <c r="CB19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="CH19">
+      <c r="CC19">
+        <v>268</v>
+      </c>
+      <c r="CD19">
         <v>2021</v>
       </c>
-      <c r="CK19" t="s">
+      <c r="CG19" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH19" s="3">
+        <v>107.0742</v>
+      </c>
+      <c r="CI19" s="3">
+        <v>0.51770000000000005</v>
+      </c>
+      <c r="CJ19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL19" s="5">
+        <v>38.04</v>
+      </c>
+      <c r="CM19" s="5">
+        <v>-28.648</v>
+      </c>
+      <c r="CP19" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="CQ19" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="CR19" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS19" s="14">
+        <v>156.6499</v>
+      </c>
+      <c r="CT19" s="15">
+        <v>0.70120000000000005</v>
+      </c>
+      <c r="CU19" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV19" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW19" s="15">
+        <v>4.28</v>
+      </c>
+      <c r="CX19" s="17">
+        <v>-22.381</v>
+      </c>
+    </row>
+    <row r="20" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>8</v>
+      </c>
+      <c r="B20" s="13">
+        <v>44493</v>
+      </c>
+      <c r="C20">
+        <v>-3.3</v>
+      </c>
+      <c r="D20">
+        <v>1.8</v>
+      </c>
+      <c r="E20">
+        <v>-10.5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>227</v>
+      </c>
+      <c r="G20">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H20">
+        <v>3.6</v>
+      </c>
+      <c r="I20">
+        <v>0.6</v>
+      </c>
+      <c r="J20">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K20" t="s">
+        <v>227</v>
+      </c>
+      <c r="L20" t="s">
+        <v>227</v>
+      </c>
+      <c r="M20">
+        <v>1.7</v>
+      </c>
+      <c r="N20">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O20" t="s">
+        <v>228</v>
+      </c>
+      <c r="P20" s="49">
+        <v>44493</v>
+      </c>
+      <c r="R20">
+        <v>1.7893817847507101</v>
+      </c>
+      <c r="S20" t="s">
+        <v>37</v>
+      </c>
+      <c r="T20" t="s">
         <v>232</v>
       </c>
-      <c r="CL19" s="3">
-        <v>107.0742</v>
-      </c>
-      <c r="CM19" s="3">
-        <v>0.51770000000000005</v>
-      </c>
-      <c r="CN19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP19" s="5">
-        <v>38.04</v>
-      </c>
-      <c r="CQ19" s="5">
-        <v>-28.648</v>
-      </c>
-      <c r="CT19" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="CU19" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="CV19" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW19" s="14">
-        <v>156.6499</v>
-      </c>
-      <c r="CX19" s="15">
-        <v>0.70120000000000005</v>
-      </c>
-      <c r="CY19" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="CZ19" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="DA19" s="15">
-        <v>4.28</v>
-      </c>
-      <c r="DB19" s="17">
-        <v>-22.381</v>
+      <c r="U20" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="V20" s="45">
+        <v>4.46</v>
+      </c>
+      <c r="W20" s="45">
+        <v>27.92</v>
+      </c>
+      <c r="X20" s="45">
+        <v>26.7</v>
+      </c>
+      <c r="Y20" s="45">
+        <v>5.39</v>
+      </c>
+      <c r="Z20" s="45">
+        <v>0.42</v>
+      </c>
+      <c r="AA20" s="45">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="AB20" s="45">
+        <v>4.75</v>
+      </c>
+      <c r="AC20" s="45">
+        <v>948.79300000000001</v>
+      </c>
+      <c r="AL20" s="45">
+        <v>1100.3516</v>
+      </c>
+      <c r="AN20" s="45">
+        <v>-13.098112</v>
+      </c>
+      <c r="AP20" s="46"/>
+      <c r="AQ20" s="46"/>
+      <c r="AR20" s="46"/>
+      <c r="AS20" s="46"/>
+      <c r="BB20" s="47"/>
+      <c r="BC20" s="47"/>
+      <c r="BD20" s="47">
+        <f t="shared" si="2"/>
+        <v>4.46</v>
+      </c>
+      <c r="BF20" s="47">
+        <f t="shared" si="3"/>
+        <v>26.7</v>
+      </c>
+      <c r="BV20" s="47">
+        <f t="shared" si="4"/>
+        <v>-13.098112</v>
+      </c>
+      <c r="BZ20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="CA20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="CB20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="CC20">
+        <v>297</v>
+      </c>
+      <c r="CD20">
+        <v>2021</v>
+      </c>
+      <c r="CG20" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH20" s="3">
+        <v>105.9919</v>
+      </c>
+      <c r="CI20" s="3">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="CJ20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL20" s="3">
+        <v>17.95</v>
+      </c>
+      <c r="CM20" s="5">
+        <v>-28.568000000000001</v>
+      </c>
+      <c r="CP20" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="CQ20" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="CR20" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS20" s="14">
+        <v>102.68049999999999</v>
+      </c>
+      <c r="CT20" s="15">
+        <v>0.46639999999999998</v>
+      </c>
+      <c r="CU20" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV20" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW20" s="15">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="CX20" s="17">
+        <v>-19.686</v>
       </c>
     </row>
-    <row r="20" spans="16:106" x14ac:dyDescent="0.2">
-      <c r="P20" s="13">
+    <row r="21" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>9</v>
+      </c>
+      <c r="B21" s="13">
         <v>44684</v>
       </c>
-      <c r="R20" s="2">
-        <v>2.4860604880000001</v>
-      </c>
-      <c r="S20">
+      <c r="C21">
+        <v>1.7</v>
+      </c>
+      <c r="D21">
+        <v>8</v>
+      </c>
+      <c r="E21">
+        <v>-6.9</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>-0.5</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" t="s">
+        <v>227</v>
+      </c>
+      <c r="J21">
+        <v>3.3</v>
+      </c>
+      <c r="K21" t="s">
+        <v>227</v>
+      </c>
+      <c r="L21" t="s">
+        <v>227</v>
+      </c>
+      <c r="M21">
+        <v>2.8</v>
+      </c>
+      <c r="N21">
+        <v>11.2</v>
+      </c>
+      <c r="O21" t="s">
+        <v>229</v>
+      </c>
+      <c r="P21" s="49">
+        <v>44684</v>
+      </c>
+      <c r="R21">
+        <v>2.3396154634610702</v>
+      </c>
+      <c r="S21" t="s">
+        <v>37</v>
+      </c>
+      <c r="T21" t="s">
+        <v>232</v>
+      </c>
+      <c r="U21" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="V21" s="45">
+        <v>4.76</v>
+      </c>
+      <c r="W21" s="45">
+        <v>21.62</v>
+      </c>
+      <c r="X21" s="45">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="Y21" s="45">
+        <v>4.59</v>
+      </c>
+      <c r="Z21" s="45">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AA21" s="45">
+        <v>7.01</v>
+      </c>
+      <c r="AB21" s="45">
+        <v>3.31</v>
+      </c>
+      <c r="AC21" s="45">
+        <v>804.30600000000004</v>
+      </c>
+      <c r="AL21" s="45">
+        <v>760</v>
+      </c>
+      <c r="AN21" s="45">
+        <v>-13.816157</v>
+      </c>
+      <c r="AP21" s="46">
+        <v>1.1802338542103299</v>
+      </c>
+      <c r="AQ21" s="46">
+        <v>1339.4732612269499</v>
+      </c>
+      <c r="AR21" s="46"/>
+      <c r="AS21" s="46">
+        <v>1.1801029868711099</v>
+      </c>
+      <c r="BB21" s="47">
         <f t="shared" si="0"/>
-        <v>214.79562616320004</v>
-      </c>
-      <c r="T20">
+        <v>1.1801029868711099</v>
+      </c>
+      <c r="BC21" s="47">
         <f t="shared" si="1"/>
-        <v>1.7899635513600004E-4</v>
-      </c>
-      <c r="U20" t="s">
-        <v>37</v>
-      </c>
-      <c r="V20">
+        <v>1.1802338542103299</v>
+      </c>
+      <c r="BD21" s="47">
         <f t="shared" si="2"/>
-        <v>1.7899635513600004E-4</v>
-      </c>
-      <c r="W20" t="s">
-        <v>233</v>
-      </c>
-      <c r="X20" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y20" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z20" s="45">
-        <v>4.46</v>
-      </c>
-      <c r="AA20" s="45">
-        <v>27.92</v>
-      </c>
-      <c r="AB20" s="45">
-        <v>26.7</v>
-      </c>
-      <c r="AC20" s="45">
-        <v>5.39</v>
-      </c>
-      <c r="AD20" s="45">
-        <v>0.42</v>
-      </c>
-      <c r="AE20" s="45">
-        <v>8.0500000000000007</v>
-      </c>
-      <c r="AF20" s="45">
-        <v>4.75</v>
-      </c>
-      <c r="AG20" s="45">
-        <v>948.79300000000001</v>
-      </c>
-      <c r="AP20" s="45">
-        <v>1100.3516</v>
-      </c>
-      <c r="AR20" s="45">
-        <v>-13.098112</v>
-      </c>
-      <c r="AT20" s="46"/>
-      <c r="AU20" s="46"/>
-      <c r="AV20" s="46"/>
-      <c r="AW20" s="46"/>
-      <c r="BF20" s="47"/>
-      <c r="BG20" s="47"/>
-      <c r="BH20" s="47">
-        <f t="shared" si="5"/>
-        <v>4.46</v>
-      </c>
-      <c r="BJ20" s="47">
-        <f t="shared" si="6"/>
-        <v>26.7</v>
-      </c>
-      <c r="BZ20" s="47">
-        <f t="shared" si="7"/>
-        <v>-13.098112</v>
-      </c>
-      <c r="CD20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="CE20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="CF20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="CH20">
-        <v>2021</v>
-      </c>
-      <c r="CK20" t="s">
-        <v>232</v>
-      </c>
-      <c r="CL20" s="3">
-        <v>105.9919</v>
-      </c>
-      <c r="CM20" s="3">
-        <v>0.46899999999999997</v>
-      </c>
-      <c r="CN20" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO20" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP20" s="3">
-        <v>17.95</v>
-      </c>
-      <c r="CQ20" s="5">
-        <v>-28.568000000000001</v>
-      </c>
-      <c r="CT20" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="CU20" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="CV20" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW20" s="14">
-        <v>102.68049999999999</v>
-      </c>
-      <c r="CX20" s="15">
-        <v>0.46639999999999998</v>
-      </c>
-      <c r="CY20" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="CZ20" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="DA20" s="15">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="DB20" s="17">
-        <v>-19.686</v>
-      </c>
-    </row>
-    <row r="21" spans="16:106" x14ac:dyDescent="0.2">
-      <c r="P21" s="13">
-        <v>44858</v>
-      </c>
-      <c r="R21" s="2">
-        <v>3.2466057350000002</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="0"/>
-        <v>280.50673550400001</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="1"/>
-        <v>2.3375561292000001E-4</v>
-      </c>
-      <c r="U21" t="s">
-        <v>37</v>
-      </c>
-      <c r="V21">
-        <f t="shared" si="2"/>
-        <v>2.3375561292000001E-4</v>
-      </c>
-      <c r="W21" t="s">
-        <v>233</v>
-      </c>
-      <c r="X21" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y21" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z21" s="45">
         <v>4.76</v>
-      </c>
-      <c r="AA21" s="45">
-        <v>21.62</v>
-      </c>
-      <c r="AB21" s="45">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="AC21" s="45">
-        <v>4.59</v>
-      </c>
-      <c r="AD21" s="45">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AE21" s="45">
-        <v>7.01</v>
-      </c>
-      <c r="AF21" s="45">
-        <v>3.31</v>
-      </c>
-      <c r="AG21" s="45">
-        <v>804.30600000000004</v>
-      </c>
-      <c r="AP21" s="45">
-        <v>760</v>
-      </c>
-      <c r="AR21" s="45">
-        <v>-13.816157</v>
-      </c>
-      <c r="AT21" s="46">
-        <v>1.1802338542103299</v>
-      </c>
-      <c r="AU21" s="46">
-        <v>1339.4732612269499</v>
-      </c>
-      <c r="AV21" s="46"/>
-      <c r="AW21" s="46">
-        <v>1.1801029868711099</v>
       </c>
       <c r="BF21" s="47">
         <f t="shared" si="3"/>
-        <v>1.1801029868711099</v>
-      </c>
-      <c r="BG21" s="47">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="BV21" s="47">
         <f t="shared" si="4"/>
-        <v>1.1802338542103299</v>
-      </c>
-      <c r="BH21" s="47">
-        <f t="shared" si="5"/>
-        <v>4.76</v>
-      </c>
-      <c r="BJ21" s="47">
-        <f t="shared" si="6"/>
-        <v>18.100000000000001</v>
-      </c>
-      <c r="BZ21" s="47">
-        <f t="shared" si="7"/>
         <v>-13.816157</v>
       </c>
-      <c r="CD21" s="2" t="s">
+      <c r="BZ21" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="CE21" s="1" t="s">
+      <c r="CA21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="CF21" s="1" t="s">
+      <c r="CB21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="CH21">
+      <c r="CC21">
+        <v>123</v>
+      </c>
+      <c r="CD21">
         <v>2022</v>
       </c>
-      <c r="CK21" t="s">
+      <c r="CG21" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH21" s="3">
+        <v>106.0802</v>
+      </c>
+      <c r="CI21" s="3">
+        <v>0.46560000000000001</v>
+      </c>
+      <c r="CJ21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL21" s="3">
+        <v>14.29</v>
+      </c>
+      <c r="CM21" s="5">
+        <v>-28.599</v>
+      </c>
+      <c r="CP21" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="CQ21" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="CR21" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS21" s="14">
+        <v>101.8574</v>
+      </c>
+      <c r="CT21" s="15">
+        <v>0.45329999999999998</v>
+      </c>
+      <c r="CU21" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV21" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW21" s="15">
+        <v>2.78</v>
+      </c>
+      <c r="CX21" s="17">
+        <v>-22.506</v>
+      </c>
+    </row>
+    <row r="22" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>10</v>
+      </c>
+      <c r="B22" s="13">
+        <v>44796</v>
+      </c>
+      <c r="C22">
+        <v>11.4</v>
+      </c>
+      <c r="D22">
+        <v>20.9</v>
+      </c>
+      <c r="E22">
+        <v>0.9</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>13.4</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="J22">
+        <v>10</v>
+      </c>
+      <c r="K22" t="s">
+        <v>227</v>
+      </c>
+      <c r="L22" t="s">
+        <v>227</v>
+      </c>
+      <c r="M22">
+        <v>0.7</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22" t="s">
+        <v>229</v>
+      </c>
+      <c r="P22" s="49">
+        <v>44796</v>
+      </c>
+      <c r="R22">
+        <v>0.20586654312220601</v>
+      </c>
+      <c r="S22" t="s">
+        <v>37</v>
+      </c>
+      <c r="T22" t="s">
         <v>232</v>
       </c>
-      <c r="CL21" s="3">
-        <v>106.0802</v>
-      </c>
-      <c r="CM21" s="3">
-        <v>0.46560000000000001</v>
-      </c>
-      <c r="CN21" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO21" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP21" s="3">
-        <v>14.29</v>
-      </c>
-      <c r="CQ21" s="5">
-        <v>-28.599</v>
-      </c>
-      <c r="CT21" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="CU21" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="CV21" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW21" s="14">
-        <v>101.8574</v>
-      </c>
-      <c r="CX21" s="15">
-        <v>0.45329999999999998</v>
-      </c>
-      <c r="CY21" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="CZ21" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="DA21" s="15">
-        <v>2.78</v>
-      </c>
-      <c r="DB21" s="17">
-        <v>-22.506</v>
-      </c>
-    </row>
-    <row r="22" spans="16:106" x14ac:dyDescent="0.2">
-      <c r="P22" s="13">
-        <v>44796</v>
-      </c>
-      <c r="R22" s="2">
-        <v>0.28571106600000001</v>
-      </c>
-      <c r="S22">
+      <c r="U22" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="V22" s="41">
+        <v>5.2249999999999996</v>
+      </c>
+      <c r="W22" s="41">
+        <v>29.895</v>
+      </c>
+      <c r="X22" s="41">
+        <v>32.049999999999997</v>
+      </c>
+      <c r="Y22" s="41">
+        <v>4.6050000000000004</v>
+      </c>
+      <c r="Z22" s="41">
+        <v>0.55499999999999994</v>
+      </c>
+      <c r="AA22" s="41">
+        <v>6.86</v>
+      </c>
+      <c r="AB22" s="41">
+        <v>7.3149999999999995</v>
+      </c>
+      <c r="AC22" s="41">
+        <v>887.99499999999989</v>
+      </c>
+      <c r="AL22" s="41">
+        <v>3050</v>
+      </c>
+      <c r="AN22" s="41">
+        <v>-13.121255999999999</v>
+      </c>
+      <c r="AP22" s="41">
+        <v>4.1224182487809102</v>
+      </c>
+      <c r="AQ22" s="41">
+        <v>8613.0523983216499</v>
+      </c>
+      <c r="AR22" s="41">
+        <v>31.387569778638358</v>
+      </c>
+      <c r="AS22" s="41">
+        <v>5.8290880669362704</v>
+      </c>
+      <c r="BB22" s="47">
         <f t="shared" si="0"/>
-        <v>24.685436102400001</v>
-      </c>
-      <c r="T22">
+        <v>5.8290880669362704</v>
+      </c>
+      <c r="BC22" s="47">
         <f t="shared" si="1"/>
-        <v>2.0571196752000001E-5</v>
-      </c>
-      <c r="U22" t="s">
-        <v>37</v>
-      </c>
-      <c r="V22">
+        <v>4.1224182487809102</v>
+      </c>
+      <c r="BD22" s="47">
         <f t="shared" si="2"/>
-        <v>2.0571196752000001E-5</v>
-      </c>
-      <c r="W22" t="s">
-        <v>233</v>
-      </c>
-      <c r="X22" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y22" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z22" s="41">
         <v>5.2249999999999996</v>
-      </c>
-      <c r="AA22" s="41">
-        <v>29.895</v>
-      </c>
-      <c r="AB22" s="41">
-        <v>32.049999999999997</v>
-      </c>
-      <c r="AC22" s="41">
-        <v>4.6050000000000004</v>
-      </c>
-      <c r="AD22" s="41">
-        <v>0.55499999999999994</v>
-      </c>
-      <c r="AE22" s="41">
-        <v>6.86</v>
-      </c>
-      <c r="AF22" s="41">
-        <v>7.3149999999999995</v>
-      </c>
-      <c r="AG22" s="41">
-        <v>887.99499999999989</v>
-      </c>
-      <c r="AP22" s="41">
-        <v>3050</v>
-      </c>
-      <c r="AR22" s="41">
-        <v>-13.121255999999999</v>
-      </c>
-      <c r="AT22" s="41">
-        <v>4.1224182487809102</v>
-      </c>
-      <c r="AU22" s="41">
-        <v>8613.0523983216499</v>
-      </c>
-      <c r="AV22" s="41">
-        <v>31.387569778638358</v>
-      </c>
-      <c r="AW22" s="41">
-        <v>5.8290880669362704</v>
       </c>
       <c r="BF22" s="47">
         <f t="shared" si="3"/>
-        <v>5.8290880669362704</v>
-      </c>
-      <c r="BG22" s="47">
+        <v>32.049999999999997</v>
+      </c>
+      <c r="BV22" s="47">
         <f t="shared" si="4"/>
-        <v>4.1224182487809102</v>
-      </c>
-      <c r="BH22" s="47">
-        <f t="shared" si="5"/>
-        <v>5.2249999999999996</v>
-      </c>
-      <c r="BJ22" s="47">
-        <f t="shared" si="6"/>
-        <v>32.049999999999997</v>
-      </c>
-      <c r="BZ22" s="47">
-        <f t="shared" si="7"/>
         <v>-13.121255999999999</v>
       </c>
-      <c r="CD22" s="2" t="s">
+      <c r="BZ22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="CE22" s="1" t="s">
+      <c r="CA22" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="CF22" s="1" t="s">
+      <c r="CB22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="CH22">
+      <c r="CC22">
+        <v>235</v>
+      </c>
+      <c r="CD22">
         <v>2022</v>
       </c>
-      <c r="CK22" t="s">
+      <c r="CG22" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH22" s="7">
+        <v>106.7341</v>
+      </c>
+      <c r="CI22" s="7">
+        <v>0.48870000000000002</v>
+      </c>
+      <c r="CJ22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL22" s="7">
+        <v>29.1</v>
+      </c>
+      <c r="CM22" s="7">
+        <v>-28.565999999999999</v>
+      </c>
+      <c r="CP22" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="CQ22" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="CR22" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS22" s="15">
+        <v>103.3593</v>
+      </c>
+      <c r="CT22" s="15">
+        <v>0.47410000000000002</v>
+      </c>
+      <c r="CU22" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CV22" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW22" s="15">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="CX22" s="17">
+        <v>-23.456</v>
+      </c>
+    </row>
+    <row r="23" spans="1:102" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23" s="13">
+        <v>44858</v>
+      </c>
+      <c r="C23">
+        <v>-3.5</v>
+      </c>
+      <c r="D23">
+        <v>0.4</v>
+      </c>
+      <c r="E23">
+        <v>-9.4</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1.4</v>
+      </c>
+      <c r="H23">
+        <v>0.4</v>
+      </c>
+      <c r="I23" t="s">
+        <v>227</v>
+      </c>
+      <c r="J23">
+        <v>4.2</v>
+      </c>
+      <c r="K23" t="s">
+        <v>227</v>
+      </c>
+      <c r="L23" t="s">
+        <v>227</v>
+      </c>
+      <c r="M23">
+        <v>0.3</v>
+      </c>
+      <c r="N23">
+        <v>2.5</v>
+      </c>
+      <c r="O23" t="s">
+        <v>229</v>
+      </c>
+      <c r="P23" s="49">
+        <v>44858</v>
+      </c>
+      <c r="R23">
+        <v>0.26120649919613098</v>
+      </c>
+      <c r="S23" t="s">
+        <v>37</v>
+      </c>
+      <c r="T23" t="s">
         <v>232</v>
       </c>
-      <c r="CL22" s="7">
-        <v>106.7341</v>
-      </c>
-      <c r="CM22" s="7">
-        <v>0.48870000000000002</v>
-      </c>
-      <c r="CN22" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO22" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP22" s="7">
-        <v>29.1</v>
-      </c>
-      <c r="CQ22" s="7">
-        <v>-28.565999999999999</v>
-      </c>
-      <c r="CT22" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="CU22" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="CV22" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="CW22" s="15">
-        <v>103.3593</v>
-      </c>
-      <c r="CX22" s="15">
-        <v>0.47410000000000002</v>
-      </c>
-      <c r="CY22" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="CZ22" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="DA22" s="15">
-        <v>5.0199999999999996</v>
-      </c>
-      <c r="DB22" s="17">
-        <v>-23.456</v>
-      </c>
-    </row>
-    <row r="23" spans="16:106" x14ac:dyDescent="0.2">
-      <c r="P23" s="13">
-        <v>44858</v>
-      </c>
-      <c r="R23" s="2">
-        <v>0.56017182700000001</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="0"/>
-        <v>48.398845852800001</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="1"/>
-        <v>4.0332371544E-5</v>
-      </c>
-      <c r="U23" t="s">
+      <c r="U23" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="V23">
-        <f t="shared" si="2"/>
-        <v>4.0332371544E-5</v>
-      </c>
-      <c r="W23" t="s">
-        <v>233</v>
-      </c>
-      <c r="X23" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y23" s="44" t="s">
+      <c r="V23" s="45">
+        <v>5.05</v>
+      </c>
+      <c r="W23" s="45">
+        <v>24.8</v>
+      </c>
+      <c r="X23" s="45">
+        <v>19.7</v>
+      </c>
+      <c r="Y23" s="45">
+        <v>4.12</v>
+      </c>
+      <c r="Z23" s="45">
+        <v>0.32</v>
+      </c>
+      <c r="AA23" s="45">
+        <v>5.89</v>
+      </c>
+      <c r="AB23" s="45">
+        <v>3.64</v>
+      </c>
+      <c r="AC23" s="45">
+        <v>661.05200000000002</v>
+      </c>
+      <c r="AL23" s="45">
+        <v>1600</v>
+      </c>
+      <c r="AN23" s="45">
+        <v>-12.954162</v>
+      </c>
+      <c r="AP23" s="46"/>
+      <c r="AQ23" s="46"/>
+      <c r="AR23" s="46"/>
+      <c r="AS23" s="46"/>
+      <c r="BB23" s="47"/>
+      <c r="BC23" s="47"/>
+      <c r="BV23" s="47">
+        <f t="shared" si="4"/>
+        <v>-12.954162</v>
+      </c>
+      <c r="BZ23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="Z23" s="45">
-        <v>5.05</v>
-      </c>
-      <c r="AA23" s="45">
-        <v>24.8</v>
-      </c>
-      <c r="AB23" s="45">
-        <v>19.7</v>
-      </c>
-      <c r="AC23" s="45">
-        <v>4.12</v>
-      </c>
-      <c r="AD23" s="45">
-        <v>0.32</v>
-      </c>
-      <c r="AE23" s="45">
-        <v>5.89</v>
-      </c>
-      <c r="AF23" s="45">
-        <v>3.64</v>
-      </c>
-      <c r="AG23" s="45">
-        <v>661.05200000000002</v>
-      </c>
-      <c r="AP23" s="45">
-        <v>1600</v>
-      </c>
-      <c r="AR23" s="45">
-        <v>-12.954162</v>
-      </c>
-      <c r="AT23" s="46"/>
-      <c r="AU23" s="46"/>
-      <c r="AV23" s="46"/>
-      <c r="AW23" s="46"/>
-      <c r="BF23" s="47"/>
-      <c r="BG23" s="47"/>
-      <c r="BZ23" s="47">
-        <f t="shared" si="7"/>
-        <v>-12.954162</v>
-      </c>
-      <c r="CD23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="CE23" s="1" t="s">
+      <c r="CA23" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="CF23" s="1" t="s">
+      <c r="CB23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="CH23">
+      <c r="CC23">
+        <v>297</v>
+      </c>
+      <c r="CD23">
         <v>2022</v>
       </c>
-      <c r="CK23" t="s">
-        <v>232</v>
+      <c r="CG23" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH23" s="3">
+        <v>105.0912</v>
+      </c>
+      <c r="CI23" s="3">
+        <v>0.48170000000000002</v>
+      </c>
+      <c r="CJ23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CK23" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="CL23" s="3">
-        <v>105.0912</v>
-      </c>
-      <c r="CM23" s="3">
-        <v>0.48170000000000002</v>
-      </c>
-      <c r="CN23" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CO23" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP23" s="3">
         <v>18.899999999999999</v>
       </c>
-      <c r="CQ23" s="5">
+      <c r="CM23" s="5">
         <v>-28.283999999999999</v>
       </c>
     </row>
